--- a/research/traditional_assets/database/data/norway/norway_aerospace_defense.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_aerospace_defense.xlsx
@@ -1534,7 +1534,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1671,22 +1671,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08436873256272705</v>
+        <v>0.08421822135108904</v>
       </c>
       <c r="C2">
-        <v>20142.32972632983</v>
+        <v>20015.91329780794</v>
       </c>
       <c r="D2">
-        <v>19465.62972632983</v>
+        <v>19541.89029780794</v>
       </c>
       <c r="E2">
-        <v>-448.6</v>
+        <v>-245.9230000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>202.677</v>
       </c>
       <c r="G2">
         <v>676.7</v>
@@ -1707,28 +1707,28 @@
         <v>510.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>10.1946531</v>
       </c>
       <c r="N2">
-        <v>510.1</v>
+        <v>499.9053469</v>
       </c>
       <c r="O2">
-        <v>112.222</v>
+        <v>109.979176318</v>
       </c>
       <c r="P2">
-        <v>397.878</v>
+        <v>389.926170582</v>
       </c>
       <c r="Q2">
-        <v>536.078</v>
+        <v>528.126170582</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08436873256272705</v>
+        <v>0.08467260742534247</v>
       </c>
       <c r="T2">
-        <v>0.890732853642657</v>
+        <v>0.8977507488531749</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>50.0360331044516</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1753,22 +1753,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08421822135108904</v>
+        <v>0.08406771013945104</v>
       </c>
       <c r="C3">
-        <v>20015.91329780794</v>
+        <v>19890.09675211006</v>
       </c>
       <c r="D3">
-        <v>19541.89029780794</v>
+        <v>19618.75075211006</v>
       </c>
       <c r="E3">
-        <v>-245.9230000000001</v>
+        <v>-43.24600000000009</v>
       </c>
       <c r="F3">
-        <v>202.677</v>
+        <v>405.3539999999999</v>
       </c>
       <c r="G3">
         <v>676.7</v>
@@ -1789,28 +1789,28 @@
         <v>510.1</v>
       </c>
       <c r="M3">
-        <v>10.1946531</v>
+        <v>20.3893062</v>
       </c>
       <c r="N3">
-        <v>499.9053469</v>
+        <v>489.7106937999999</v>
       </c>
       <c r="O3">
-        <v>109.979176318</v>
+        <v>107.736352636</v>
       </c>
       <c r="P3">
-        <v>389.926170582</v>
+        <v>381.974341164</v>
       </c>
       <c r="Q3">
-        <v>528.126170582</v>
+        <v>520.174341164</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08467260742534247</v>
+        <v>0.08498268381576637</v>
       </c>
       <c r="T3">
-        <v>0.8977507488531749</v>
+        <v>0.9049118664149278</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>50.0360331044516</v>
+        <v>25.0180165522258</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1835,22 +1835,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08406771013945104</v>
+        <v>0.08391719892781305</v>
       </c>
       <c r="C4">
-        <v>19890.09675211006</v>
+        <v>19764.88719540556</v>
       </c>
       <c r="D4">
-        <v>19618.75075211006</v>
+        <v>19696.21819540556</v>
       </c>
       <c r="E4">
-        <v>-43.24600000000009</v>
+        <v>159.4309999999998</v>
       </c>
       <c r="F4">
-        <v>405.3539999999999</v>
+        <v>608.0309999999998</v>
       </c>
       <c r="G4">
         <v>676.7</v>
@@ -1871,28 +1871,28 @@
         <v>510.1</v>
       </c>
       <c r="M4">
-        <v>20.3893062</v>
+        <v>30.58395929999999</v>
       </c>
       <c r="N4">
-        <v>489.7106937999999</v>
+        <v>479.5160407</v>
       </c>
       <c r="O4">
-        <v>107.736352636</v>
+        <v>105.493528954</v>
       </c>
       <c r="P4">
-        <v>381.974341164</v>
+        <v>374.022511746</v>
       </c>
       <c r="Q4">
-        <v>520.174341164</v>
+        <v>512.222511746</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08498268381576637</v>
+        <v>0.08529915353382789</v>
       </c>
       <c r="T4">
-        <v>0.9049118664149278</v>
+        <v>0.9122206358851705</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>25.0180165522258</v>
+        <v>16.67867770148387</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1917,22 +1917,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08391719892781305</v>
+        <v>0.08376668771617504</v>
       </c>
       <c r="C5">
-        <v>19764.88719540556</v>
+        <v>19640.29184654771</v>
       </c>
       <c r="D5">
-        <v>19696.21819540556</v>
+        <v>19774.2998465477</v>
       </c>
       <c r="E5">
-        <v>159.4309999999998</v>
+        <v>362.1079999999998</v>
       </c>
       <c r="F5">
-        <v>608.0309999999998</v>
+        <v>810.7079999999999</v>
       </c>
       <c r="G5">
         <v>676.7</v>
@@ -1953,28 +1953,28 @@
         <v>510.1</v>
       </c>
       <c r="M5">
-        <v>30.58395929999999</v>
+        <v>40.77861239999999</v>
       </c>
       <c r="N5">
-        <v>479.5160407</v>
+        <v>469.3213876</v>
       </c>
       <c r="O5">
-        <v>105.493528954</v>
+        <v>103.250705272</v>
       </c>
       <c r="P5">
-        <v>374.022511746</v>
+        <v>366.070682328</v>
       </c>
       <c r="Q5">
-        <v>512.222511746</v>
+        <v>504.270682328</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08529915353382789</v>
+        <v>0.08562221637101566</v>
       </c>
       <c r="T5">
-        <v>0.9122206358851705</v>
+        <v>0.9196816713860433</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>16.67867770148387</v>
+        <v>12.5090082761129</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1999,22 +1999,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08376668771617504</v>
+        <v>0.08361617650453704</v>
       </c>
       <c r="C6">
-        <v>19640.29184654771</v>
+        <v>19516.31803931601</v>
       </c>
       <c r="D6">
-        <v>19774.2998465477</v>
+        <v>19853.00303931601</v>
       </c>
       <c r="E6">
-        <v>362.1079999999998</v>
+        <v>564.7849999999999</v>
       </c>
       <c r="F6">
-        <v>810.7079999999999</v>
+        <v>1013.385</v>
       </c>
       <c r="G6">
         <v>676.7</v>
@@ -2035,28 +2035,28 @@
         <v>510.1</v>
       </c>
       <c r="M6">
-        <v>40.77861239999999</v>
+        <v>50.97326549999999</v>
       </c>
       <c r="N6">
-        <v>469.3213876</v>
+        <v>459.1267345</v>
       </c>
       <c r="O6">
-        <v>103.250705272</v>
+        <v>101.00788159</v>
       </c>
       <c r="P6">
-        <v>366.070682328</v>
+        <v>358.11885291</v>
       </c>
       <c r="Q6">
-        <v>504.270682328</v>
+        <v>496.31885291</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08562221637101566</v>
+        <v>0.08595208053109163</v>
       </c>
       <c r="T6">
-        <v>0.9196816713860433</v>
+        <v>0.9272997813185135</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2073,7 +2073,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>12.5090082761129</v>
+        <v>10.00720662089032</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08361617650453704</v>
+        <v>0.08353586529289904</v>
       </c>
       <c r="C7">
-        <v>19516.31803931601</v>
+        <v>19355.89311744818</v>
       </c>
       <c r="D7">
-        <v>19853.00303931601</v>
+        <v>19895.25511744818</v>
       </c>
       <c r="E7">
-        <v>564.7849999999999</v>
+        <v>767.4619999999999</v>
       </c>
       <c r="F7">
-        <v>1013.385</v>
+        <v>1216.062</v>
       </c>
       <c r="G7">
         <v>676.7</v>
@@ -2117,45 +2117,45 @@
         <v>510.1</v>
       </c>
       <c r="M7">
-        <v>50.97326549999999</v>
+        <v>62.99201159999999</v>
       </c>
       <c r="N7">
-        <v>459.1267345</v>
+        <v>447.1079884</v>
       </c>
       <c r="O7">
-        <v>101.00788159</v>
+        <v>98.36375744799999</v>
       </c>
       <c r="P7">
-        <v>358.11885291</v>
+        <v>348.744230952</v>
       </c>
       <c r="Q7">
-        <v>496.31885291</v>
+        <v>486.9442309519999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08595208053109163</v>
+        <v>0.08628896307755218</v>
       </c>
       <c r="T7">
-        <v>0.9272997813185135</v>
+        <v>0.9350799786963552</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0.22</v>
       </c>
       <c r="W7">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>10.00720662089032</v>
+        <v>8.097852204484926</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2163,22 +2163,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08353586529289904</v>
+        <v>0.08339705408126105</v>
       </c>
       <c r="C8">
-        <v>19355.89311744818</v>
+        <v>19226.67092757056</v>
       </c>
       <c r="D8">
-        <v>19895.25511744818</v>
+        <v>19968.70992757056</v>
       </c>
       <c r="E8">
-        <v>767.4619999999996</v>
+        <v>970.1389999999996</v>
       </c>
       <c r="F8">
-        <v>1216.062</v>
+        <v>1418.739</v>
       </c>
       <c r="G8">
         <v>676.7</v>
@@ -2199,28 +2199,28 @@
         <v>510.1</v>
       </c>
       <c r="M8">
-        <v>62.99201159999998</v>
+        <v>73.49068019999997</v>
       </c>
       <c r="N8">
-        <v>447.1079884</v>
+        <v>436.6093198</v>
       </c>
       <c r="O8">
-        <v>98.36375744799999</v>
+        <v>96.05405035599999</v>
       </c>
       <c r="P8">
-        <v>348.744230952</v>
+        <v>340.555269444</v>
       </c>
       <c r="Q8">
-        <v>486.9442309519999</v>
+        <v>478.755269444</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08628896307755218</v>
+        <v>0.08663309040995812</v>
       </c>
       <c r="T8">
-        <v>0.9350799786963552</v>
+        <v>0.9430274921468387</v>
       </c>
       <c r="U8">
         <v>0.0518</v>
@@ -2237,7 +2237,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>8.097852204484926</v>
+        <v>6.941016175272796</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2245,22 +2245,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08339705408126105</v>
+        <v>0.08336432286962304</v>
       </c>
       <c r="C9">
-        <v>19226.67092757056</v>
+        <v>19041.39341785409</v>
       </c>
       <c r="D9">
-        <v>19968.70992757056</v>
+        <v>19986.10941785409</v>
       </c>
       <c r="E9">
-        <v>970.139</v>
+        <v>1172.816</v>
       </c>
       <c r="F9">
-        <v>1418.739</v>
+        <v>1621.416</v>
       </c>
       <c r="G9">
         <v>676.7</v>
@@ -2281,45 +2281,45 @@
         <v>510.1</v>
       </c>
       <c r="M9">
-        <v>73.4906802</v>
+        <v>86.74575599999999</v>
       </c>
       <c r="N9">
-        <v>436.6093198</v>
+        <v>423.354244</v>
       </c>
       <c r="O9">
-        <v>96.05405035599999</v>
+        <v>93.13793368</v>
       </c>
       <c r="P9">
-        <v>340.555269444</v>
+        <v>330.21631032</v>
       </c>
       <c r="Q9">
-        <v>478.755269444</v>
+        <v>468.41631032</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08663309040995812</v>
+        <v>0.08698469877132939</v>
       </c>
       <c r="T9">
-        <v>0.9430274921468389</v>
+        <v>0.9511477776288545</v>
       </c>
       <c r="U9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V9">
         <v>0.22</v>
       </c>
       <c r="W9">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>6.941016175272793</v>
+        <v>5.880402955967091</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2327,22 +2327,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08336432286962304</v>
+        <v>0.08329493165798504</v>
       </c>
       <c r="C10">
-        <v>19041.39341785409</v>
+        <v>18875.70435961339</v>
       </c>
       <c r="D10">
-        <v>19986.10941785409</v>
+        <v>20023.09735961339</v>
       </c>
       <c r="E10">
-        <v>1172.816</v>
+        <v>1375.492999999999</v>
       </c>
       <c r="F10">
-        <v>1621.416</v>
+        <v>1824.093</v>
       </c>
       <c r="G10">
         <v>676.7</v>
@@ -2363,45 +2363,45 @@
         <v>510.1</v>
       </c>
       <c r="M10">
-        <v>86.74575599999999</v>
+        <v>99.04824989999999</v>
       </c>
       <c r="N10">
-        <v>423.354244</v>
+        <v>411.0517501</v>
       </c>
       <c r="O10">
-        <v>93.13793368</v>
+        <v>90.431385022</v>
       </c>
       <c r="P10">
-        <v>330.21631032</v>
+        <v>320.620365078</v>
       </c>
       <c r="Q10">
-        <v>468.41631032</v>
+        <v>458.820365078</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08698469877132939</v>
+        <v>0.08734403478899455</v>
       </c>
       <c r="T10">
-        <v>0.9511477776288545</v>
+        <v>0.9594465309236619</v>
       </c>
       <c r="U10">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V10">
         <v>0.22</v>
       </c>
       <c r="W10">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y10">
-        <v>5.880402955967091</v>
+        <v>5.150015275534919</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2409,22 +2409,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08329493165798504</v>
+        <v>0.08317562044634706</v>
       </c>
       <c r="C11">
-        <v>18875.70435961339</v>
+        <v>18736.94549604005</v>
       </c>
       <c r="D11">
-        <v>20023.09735961339</v>
+        <v>20087.01549604005</v>
       </c>
       <c r="E11">
-        <v>1375.492999999999</v>
+        <v>1578.17</v>
       </c>
       <c r="F11">
-        <v>1824.093</v>
+        <v>2026.77</v>
       </c>
       <c r="G11">
         <v>676.7</v>
@@ -2445,28 +2445,28 @@
         <v>510.1</v>
       </c>
       <c r="M11">
-        <v>99.04824989999999</v>
+        <v>110.053611</v>
       </c>
       <c r="N11">
-        <v>411.0517501</v>
+        <v>400.046389</v>
       </c>
       <c r="O11">
-        <v>90.431385022</v>
+        <v>88.01020557999999</v>
       </c>
       <c r="P11">
-        <v>320.620365078</v>
+        <v>312.03618342</v>
       </c>
       <c r="Q11">
-        <v>458.820365078</v>
+        <v>450.23618342</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08734403478899455</v>
+        <v>0.08771135605149673</v>
       </c>
       <c r="T11">
-        <v>0.9594465309236619</v>
+        <v>0.967929700958354</v>
       </c>
       <c r="U11">
         <v>0.0543</v>
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>5.150015275534919</v>
+        <v>4.635013747981428</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2491,22 +2491,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08317562044634706</v>
+        <v>0.08314210923470905</v>
       </c>
       <c r="C12">
-        <v>18736.94549604005</v>
+        <v>18552.29480042561</v>
       </c>
       <c r="D12">
-        <v>20087.01549604005</v>
+        <v>20105.04180042561</v>
       </c>
       <c r="E12">
-        <v>1578.17</v>
+        <v>1780.847</v>
       </c>
       <c r="F12">
-        <v>2026.77</v>
+        <v>2229.447</v>
       </c>
       <c r="G12">
         <v>676.7</v>
@@ -2527,45 +2527,45 @@
         <v>510.1</v>
       </c>
       <c r="M12">
-        <v>110.053611</v>
+        <v>123.2884191</v>
       </c>
       <c r="N12">
-        <v>400.046389</v>
+        <v>386.8115809</v>
       </c>
       <c r="O12">
-        <v>88.01020557999999</v>
+        <v>85.098547798</v>
       </c>
       <c r="P12">
-        <v>312.03618342</v>
+        <v>301.7130331019999</v>
       </c>
       <c r="Q12">
-        <v>450.23618342</v>
+        <v>439.9130331019999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08771135605149673</v>
+        <v>0.08808693172439219</v>
       </c>
       <c r="T12">
-        <v>0.967929700958354</v>
+        <v>0.9766035040275335</v>
       </c>
       <c r="U12">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V12">
         <v>0.22</v>
       </c>
       <c r="W12">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y12">
-        <v>4.635013747981427</v>
+        <v>4.137452679851907</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2573,22 +2573,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08314210923470905</v>
+        <v>0.08303059802307104</v>
       </c>
       <c r="C13">
-        <v>18552.29480042561</v>
+        <v>18409.83540879733</v>
       </c>
       <c r="D13">
-        <v>20105.04180042561</v>
+        <v>20165.25940879733</v>
       </c>
       <c r="E13">
-        <v>1780.847</v>
+        <v>1983.523999999999</v>
       </c>
       <c r="F13">
-        <v>2229.447</v>
+        <v>2432.123999999999</v>
       </c>
       <c r="G13">
         <v>676.7</v>
@@ -2609,28 +2609,28 @@
         <v>510.1</v>
       </c>
       <c r="M13">
-        <v>123.2884191</v>
+        <v>134.4964572</v>
       </c>
       <c r="N13">
-        <v>386.8115809</v>
+        <v>375.6035428</v>
       </c>
       <c r="O13">
-        <v>85.098547798</v>
+        <v>82.63277941600001</v>
       </c>
       <c r="P13">
-        <v>301.7130331019999</v>
+        <v>292.970763384</v>
       </c>
       <c r="Q13">
-        <v>439.9130331019999</v>
+        <v>431.170763384</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08808693172439219</v>
+        <v>0.08847104320803528</v>
       </c>
       <c r="T13">
-        <v>0.9766035040275335</v>
+        <v>0.9854744389846487</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>4.137452679851907</v>
+        <v>3.792664956530915</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2655,22 +2655,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08303059802307104</v>
+        <v>0.08291908681143305</v>
       </c>
       <c r="C14">
-        <v>18409.83540879733</v>
+        <v>18267.73782232366</v>
       </c>
       <c r="D14">
-        <v>20165.25940879733</v>
+        <v>20225.83882232366</v>
       </c>
       <c r="E14">
-        <v>1983.523999999999</v>
+        <v>2186.201</v>
       </c>
       <c r="F14">
-        <v>2432.123999999999</v>
+        <v>2634.801</v>
       </c>
       <c r="G14">
         <v>676.7</v>
@@ -2691,28 +2691,28 @@
         <v>510.1</v>
       </c>
       <c r="M14">
-        <v>134.4964572</v>
+        <v>145.7044953</v>
       </c>
       <c r="N14">
-        <v>375.6035428</v>
+        <v>364.3955046999999</v>
       </c>
       <c r="O14">
-        <v>82.63277941600001</v>
+        <v>80.16701103399998</v>
       </c>
       <c r="P14">
-        <v>292.970763384</v>
+        <v>284.228493666</v>
       </c>
       <c r="Q14">
-        <v>431.170763384</v>
+        <v>422.428493666</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08847104320803528</v>
+        <v>0.08886398484072765</v>
       </c>
       <c r="T14">
-        <v>0.9854744389846487</v>
+        <v>0.994549303481008</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2729,7 +2729,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>3.792664956530915</v>
+        <v>3.500921498336229</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2737,22 +2737,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08291908681143305</v>
+        <v>0.08280757559979506</v>
       </c>
       <c r="C15">
-        <v>18267.73782232366</v>
+        <v>18126.00531157803</v>
       </c>
       <c r="D15">
-        <v>20225.83882232366</v>
+        <v>20286.78331157803</v>
       </c>
       <c r="E15">
-        <v>2186.201</v>
+        <v>2388.878</v>
       </c>
       <c r="F15">
-        <v>2634.801</v>
+        <v>2837.478</v>
       </c>
       <c r="G15">
         <v>676.7</v>
@@ -2773,28 +2773,28 @@
         <v>510.1</v>
       </c>
       <c r="M15">
-        <v>145.7044953</v>
+        <v>156.9125334</v>
       </c>
       <c r="N15">
-        <v>364.3955046999999</v>
+        <v>353.1874666</v>
       </c>
       <c r="O15">
-        <v>80.16701103399998</v>
+        <v>77.701242652</v>
       </c>
       <c r="P15">
-        <v>284.228493666</v>
+        <v>275.486223948</v>
       </c>
       <c r="Q15">
-        <v>422.428493666</v>
+        <v>413.686223948</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08886398484072765</v>
+        <v>0.08926606465092449</v>
       </c>
       <c r="T15">
-        <v>0.994549303481008</v>
+        <v>1.003835211337748</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2811,7 +2811,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>3.500921498336229</v>
+        <v>3.250855677026498</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2819,22 +2819,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08280757559979506</v>
+        <v>0.08269606438815706</v>
       </c>
       <c r="C16">
-        <v>18126.00531157803</v>
+        <v>17984.64118667258</v>
       </c>
       <c r="D16">
-        <v>20286.78331157803</v>
+        <v>20348.09618667258</v>
       </c>
       <c r="E16">
-        <v>2388.878</v>
+        <v>2591.555</v>
       </c>
       <c r="F16">
-        <v>2837.478</v>
+        <v>3040.155</v>
       </c>
       <c r="G16">
         <v>676.7</v>
@@ -2855,28 +2855,28 @@
         <v>510.1</v>
       </c>
       <c r="M16">
-        <v>156.9125334</v>
+        <v>168.1205715</v>
       </c>
       <c r="N16">
-        <v>353.1874666</v>
+        <v>341.9794284999999</v>
       </c>
       <c r="O16">
-        <v>77.701242652</v>
+        <v>75.23547426999998</v>
       </c>
       <c r="P16">
-        <v>275.486223948</v>
+        <v>266.7439542299999</v>
       </c>
       <c r="Q16">
-        <v>413.686223948</v>
+        <v>404.9439542299999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08926606465092449</v>
+        <v>0.08967760516253771</v>
       </c>
       <c r="T16">
-        <v>1.003835211337748</v>
+        <v>1.013339611144058</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2893,7 +2893,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>3.250855677026498</v>
+        <v>3.034131965224731</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2901,22 +2901,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08269606438815706</v>
+        <v>0.08289655317651905</v>
       </c>
       <c r="C17">
-        <v>17984.64118667258</v>
+        <v>17671.99264482806</v>
       </c>
       <c r="D17">
-        <v>20348.09618667258</v>
+        <v>20238.12464482806</v>
       </c>
       <c r="E17">
-        <v>2591.554999999999</v>
+        <v>2794.232</v>
       </c>
       <c r="F17">
-        <v>3040.154999999999</v>
+        <v>3242.831999999999</v>
       </c>
       <c r="G17">
         <v>676.7</v>
@@ -2937,45 +2937,45 @@
         <v>510.1</v>
       </c>
       <c r="M17">
-        <v>168.1205715</v>
+        <v>187.4356896</v>
       </c>
       <c r="N17">
-        <v>341.9794285</v>
+        <v>322.6643104</v>
       </c>
       <c r="O17">
-        <v>75.23547427000001</v>
+        <v>70.986148288</v>
       </c>
       <c r="P17">
-        <v>266.74395423</v>
+        <v>251.678162112</v>
       </c>
       <c r="Q17">
-        <v>404.94395423</v>
+        <v>389.878162112</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08967760516253771</v>
+        <v>0.09009894425776077</v>
       </c>
       <c r="T17">
-        <v>1.013339611144058</v>
+        <v>1.023070306183852</v>
       </c>
       <c r="U17">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V17">
         <v>0.22</v>
       </c>
       <c r="W17">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y17">
-        <v>3.034131965224732</v>
+        <v>2.721466765953628</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2983,22 +2983,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08289655317651905</v>
+        <v>0.08280454196488105</v>
       </c>
       <c r="C18">
-        <v>17671.99264482806</v>
+        <v>17519.63742347942</v>
       </c>
       <c r="D18">
-        <v>20238.12464482806</v>
+        <v>20288.44642347941</v>
       </c>
       <c r="E18">
-        <v>2794.232</v>
+        <v>2996.909</v>
       </c>
       <c r="F18">
-        <v>3242.831999999999</v>
+        <v>3445.509</v>
       </c>
       <c r="G18">
         <v>676.7</v>
@@ -3019,28 +3019,28 @@
         <v>510.1</v>
       </c>
       <c r="M18">
-        <v>187.4356896</v>
+        <v>199.1504202</v>
       </c>
       <c r="N18">
-        <v>322.6643104</v>
+        <v>310.9495798</v>
       </c>
       <c r="O18">
-        <v>70.986148288</v>
+        <v>68.408907556</v>
       </c>
       <c r="P18">
-        <v>251.678162112</v>
+        <v>242.540672244</v>
       </c>
       <c r="Q18">
-        <v>389.878162112</v>
+        <v>380.7406722439999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09009894425776077</v>
+        <v>0.09053043610226633</v>
       </c>
       <c r="T18">
-        <v>1.023070306183852</v>
+        <v>1.033035475802918</v>
       </c>
       <c r="U18">
         <v>0.0578</v>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>2.721466765953628</v>
+        <v>2.561380485603414</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3065,22 +3065,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08280454196488105</v>
+        <v>0.08320393075324306</v>
       </c>
       <c r="C19">
-        <v>17519.63742347942</v>
+        <v>17100.32602512494</v>
       </c>
       <c r="D19">
-        <v>20288.44642347941</v>
+        <v>20071.81202512494</v>
       </c>
       <c r="E19">
-        <v>2996.909</v>
+        <v>3199.586</v>
       </c>
       <c r="F19">
-        <v>3445.509</v>
+        <v>3648.186</v>
       </c>
       <c r="G19">
         <v>676.7</v>
@@ -3101,45 +3101,45 @@
         <v>510.1</v>
       </c>
       <c r="M19">
-        <v>199.1504202</v>
+        <v>223.6338018</v>
       </c>
       <c r="N19">
-        <v>310.9495798</v>
+        <v>286.4661982</v>
       </c>
       <c r="O19">
-        <v>68.408907556</v>
+        <v>63.02256360400001</v>
       </c>
       <c r="P19">
-        <v>242.540672244</v>
+        <v>223.443634596</v>
       </c>
       <c r="Q19">
-        <v>380.7406722439999</v>
+        <v>361.643634596</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09053043610226633</v>
+        <v>0.09097245213810129</v>
       </c>
       <c r="T19">
-        <v>1.033035475802918</v>
+        <v>1.043243698339522</v>
       </c>
       <c r="U19">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V19">
         <v>0.22</v>
       </c>
       <c r="W19">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>2.561380485603414</v>
+        <v>2.280961088593362</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08320393075324306</v>
+        <v>0.08355417954160504</v>
       </c>
       <c r="C20">
-        <v>17100.32602512494</v>
+        <v>16711.4410892782</v>
       </c>
       <c r="D20">
-        <v>20071.81202512494</v>
+        <v>19885.6040892782</v>
       </c>
       <c r="E20">
-        <v>3199.585999999999</v>
+        <v>3402.262999999999</v>
       </c>
       <c r="F20">
-        <v>3648.185999999999</v>
+        <v>3850.862999999999</v>
       </c>
       <c r="G20">
         <v>676.7</v>
@@ -3183,45 +3183,45 @@
         <v>510.1</v>
       </c>
       <c r="M20">
-        <v>223.6338018</v>
+        <v>246.8403183</v>
       </c>
       <c r="N20">
-        <v>286.4661982</v>
+        <v>263.2596817</v>
       </c>
       <c r="O20">
-        <v>63.02256360400001</v>
+        <v>57.917129974</v>
       </c>
       <c r="P20">
-        <v>223.443634596</v>
+        <v>205.342551726</v>
       </c>
       <c r="Q20">
-        <v>361.643634596</v>
+        <v>343.5425517259999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09097245213810129</v>
+        <v>0.09142538215012969</v>
       </c>
       <c r="T20">
-        <v>1.043243698339522</v>
+        <v>1.053703975753573</v>
       </c>
       <c r="U20">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V20">
         <v>0.22</v>
       </c>
       <c r="W20">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>2.280961088593362</v>
+        <v>2.066518158431657</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3229,22 +3229,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08355417954160504</v>
+        <v>0.08472810832996705</v>
       </c>
       <c r="C21">
-        <v>16711.4410892782</v>
+        <v>15909.08729747267</v>
       </c>
       <c r="D21">
-        <v>19885.6040892782</v>
+        <v>19285.92729747267</v>
       </c>
       <c r="E21">
-        <v>3402.262999999999</v>
+        <v>3604.94</v>
       </c>
       <c r="F21">
-        <v>3850.862999999999</v>
+        <v>4053.54</v>
       </c>
       <c r="G21">
         <v>676.7</v>
@@ -3265,45 +3265,45 @@
         <v>510.1</v>
       </c>
       <c r="M21">
-        <v>246.8403183</v>
+        <v>291.449526</v>
       </c>
       <c r="N21">
-        <v>263.2596817</v>
+        <v>218.650474</v>
       </c>
       <c r="O21">
-        <v>57.917129974</v>
+        <v>48.10310428</v>
       </c>
       <c r="P21">
-        <v>205.342551726</v>
+        <v>170.54736972</v>
       </c>
       <c r="Q21">
-        <v>343.5425517259999</v>
+        <v>308.7473697199999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09142538215012969</v>
+        <v>0.09188963541245881</v>
       </c>
       <c r="T21">
-        <v>1.053703975753573</v>
+        <v>1.064425760102975</v>
       </c>
       <c r="U21">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V21">
         <v>0.22</v>
       </c>
       <c r="W21">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>2.066518158431657</v>
+        <v>1.750217291483946</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3311,22 +3311,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08472810832996705</v>
+        <v>0.08538489711832907</v>
       </c>
       <c r="C22">
-        <v>15909.08729747267</v>
+        <v>15386.42005512643</v>
       </c>
       <c r="D22">
-        <v>19285.92729747267</v>
+        <v>18965.93705512643</v>
       </c>
       <c r="E22">
-        <v>3604.94</v>
+        <v>3807.617</v>
       </c>
       <c r="F22">
-        <v>4053.54</v>
+        <v>4256.217</v>
       </c>
       <c r="G22">
         <v>676.7</v>
@@ -3347,45 +3347,45 @@
         <v>510.1</v>
       </c>
       <c r="M22">
-        <v>291.449526</v>
+        <v>322.6212486</v>
       </c>
       <c r="N22">
-        <v>218.650474</v>
+        <v>187.4787514</v>
       </c>
       <c r="O22">
-        <v>48.10310428</v>
+        <v>41.24532530799999</v>
       </c>
       <c r="P22">
-        <v>170.54736972</v>
+        <v>146.233426092</v>
       </c>
       <c r="Q22">
-        <v>308.7473697199999</v>
+        <v>284.433426092</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09188963541245881</v>
+        <v>0.09236564192193553</v>
       </c>
       <c r="T22">
-        <v>1.064425760102975</v>
+        <v>1.075418982030844</v>
       </c>
       <c r="U22">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V22">
         <v>0.22</v>
       </c>
       <c r="W22">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y22">
-        <v>1.750217291483946</v>
+        <v>1.581110984516846</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3393,22 +3393,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08538489711832906</v>
+        <v>0.08543328590669105</v>
       </c>
       <c r="C23">
-        <v>15386.42005512644</v>
+        <v>15160.58729871481</v>
       </c>
       <c r="D23">
-        <v>18965.93705512644</v>
+        <v>18942.78129871481</v>
       </c>
       <c r="E23">
-        <v>3807.617</v>
+        <v>4010.293999999999</v>
       </c>
       <c r="F23">
-        <v>4256.217</v>
+        <v>4458.893999999999</v>
       </c>
       <c r="G23">
         <v>676.7</v>
@@ -3429,28 +3429,28 @@
         <v>510.1</v>
       </c>
       <c r="M23">
-        <v>322.6212486</v>
+        <v>337.9841651999999</v>
       </c>
       <c r="N23">
-        <v>187.4787514</v>
+        <v>172.1158348</v>
       </c>
       <c r="O23">
-        <v>41.24532530799999</v>
+        <v>37.865483656</v>
       </c>
       <c r="P23">
-        <v>146.233426092</v>
+        <v>134.250351144</v>
       </c>
       <c r="Q23">
-        <v>284.433426092</v>
+        <v>272.450351144</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09236564192193551</v>
+        <v>0.09285385372652699</v>
       </c>
       <c r="T23">
-        <v>1.075418982030843</v>
+        <v>1.086694081444042</v>
       </c>
       <c r="U23">
         <v>0.07580000000000001</v>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>1.581110984516846</v>
+        <v>1.509242303402444</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3475,22 +3475,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08543328590669105</v>
+        <v>0.09377511624281229</v>
       </c>
       <c r="C24">
-        <v>15160.58729871481</v>
+        <v>11664.17220981954</v>
       </c>
       <c r="D24">
-        <v>18942.78129871481</v>
+        <v>15649.04320981954</v>
       </c>
       <c r="E24">
-        <v>4010.293999999999</v>
+        <v>4212.971</v>
       </c>
       <c r="F24">
-        <v>4458.893999999999</v>
+        <v>4661.571</v>
       </c>
       <c r="G24">
         <v>676.7</v>
@@ -3511,45 +3511,45 @@
         <v>510.1</v>
       </c>
       <c r="M24">
-        <v>337.9841651999999</v>
+        <v>552.8623206000001</v>
       </c>
       <c r="N24">
-        <v>172.1158348</v>
+        <v>-42.76232060000012</v>
       </c>
       <c r="O24">
-        <v>37.865483656</v>
+        <v>-9.407710532000028</v>
       </c>
       <c r="P24">
-        <v>134.250351144</v>
+        <v>-33.3546100680001</v>
       </c>
       <c r="Q24">
-        <v>272.450351144</v>
+        <v>104.8453899319999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09285385372652699</v>
+        <v>0.09355078398201416</v>
       </c>
       <c r="T24">
-        <v>1.086694081444042</v>
+        <v>1.102789468406794</v>
       </c>
       <c r="U24">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V24">
-        <v>0.22</v>
+        <v>0.2029836286875362</v>
       </c>
       <c r="W24">
-        <v>0.05912400000000001</v>
+        <v>0.09452614163765823</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y24">
-        <v>1.509242303402444</v>
+        <v>0.9226528576706189</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3557,22 +3557,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09377511624281229</v>
+        <v>0.0945031162428123</v>
       </c>
       <c r="C25">
-        <v>11664.17220981954</v>
+        <v>11227.57786867959</v>
       </c>
       <c r="D25">
-        <v>15649.04320981954</v>
+        <v>15415.12586867958</v>
       </c>
       <c r="E25">
-        <v>4212.971</v>
+        <v>4415.647999999999</v>
       </c>
       <c r="F25">
-        <v>4661.571</v>
+        <v>4864.248</v>
       </c>
       <c r="G25">
         <v>676.7</v>
@@ -3593,37 +3593,37 @@
         <v>510.1</v>
       </c>
       <c r="M25">
-        <v>552.8623206000001</v>
+        <v>576.8998127999999</v>
       </c>
       <c r="N25">
-        <v>-42.76232060000012</v>
+        <v>-66.79981279999998</v>
       </c>
       <c r="O25">
-        <v>-9.407710532000028</v>
+        <v>-14.695958816</v>
       </c>
       <c r="P25">
-        <v>-33.3546100680001</v>
+        <v>-52.10385398399999</v>
       </c>
       <c r="Q25">
-        <v>104.8453899319999</v>
+        <v>86.09614601600001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09355078398201416</v>
+        <v>0.0941790837712512</v>
       </c>
       <c r="T25">
-        <v>1.102789468406794</v>
+        <v>1.117299856148988</v>
       </c>
       <c r="U25">
         <v>0.1186</v>
       </c>
       <c r="V25">
-        <v>0.2029836286875362</v>
+        <v>0.1945259774922222</v>
       </c>
       <c r="W25">
-        <v>0.09452614163765823</v>
+        <v>0.09552921906942245</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.9226528576706189</v>
+        <v>0.88420898860101</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3639,22 +3639,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0945031162428123</v>
+        <v>0.09523111624281229</v>
       </c>
       <c r="C26">
-        <v>11227.57786867959</v>
+        <v>10797.87359344523</v>
       </c>
       <c r="D26">
-        <v>15415.12586867958</v>
+        <v>15188.09859344523</v>
       </c>
       <c r="E26">
-        <v>4415.647999999998</v>
+        <v>4618.324999999999</v>
       </c>
       <c r="F26">
-        <v>4864.247999999999</v>
+        <v>5066.924999999999</v>
       </c>
       <c r="G26">
         <v>676.7</v>
@@ -3675,37 +3675,37 @@
         <v>510.1</v>
       </c>
       <c r="M26">
-        <v>576.8998127999999</v>
+        <v>600.9373049999999</v>
       </c>
       <c r="N26">
-        <v>-66.79981279999998</v>
+        <v>-90.83730499999996</v>
       </c>
       <c r="O26">
-        <v>-14.695958816</v>
+        <v>-19.98420709999999</v>
       </c>
       <c r="P26">
-        <v>-52.10385398399999</v>
+        <v>-70.85309789999997</v>
       </c>
       <c r="Q26">
-        <v>86.09614601600001</v>
+        <v>67.34690210000002</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09417908377125118</v>
+        <v>0.09482413822153454</v>
       </c>
       <c r="T26">
-        <v>1.117299856148988</v>
+        <v>1.132197187564308</v>
       </c>
       <c r="U26">
         <v>0.1186</v>
       </c>
       <c r="V26">
-        <v>0.1945259774922222</v>
+        <v>0.1867449383925333</v>
       </c>
       <c r="W26">
-        <v>0.09552921906942245</v>
+        <v>0.09645205030664555</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.88420898860101</v>
+        <v>0.8488406290569697</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3721,22 +3721,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09523111624281229</v>
+        <v>0.09595911624281231</v>
       </c>
       <c r="C27">
-        <v>10797.87359344523</v>
+        <v>10374.75938074587</v>
       </c>
       <c r="D27">
-        <v>15188.09859344523</v>
+        <v>14967.66138074587</v>
       </c>
       <c r="E27">
-        <v>4618.324999999999</v>
+        <v>4821.001999999999</v>
       </c>
       <c r="F27">
-        <v>5066.924999999999</v>
+        <v>5269.602</v>
       </c>
       <c r="G27">
         <v>676.7</v>
@@ -3757,37 +3757,37 @@
         <v>510.1</v>
       </c>
       <c r="M27">
-        <v>600.9373049999999</v>
+        <v>624.9747972</v>
       </c>
       <c r="N27">
-        <v>-90.83730499999996</v>
+        <v>-114.8747972</v>
       </c>
       <c r="O27">
-        <v>-19.98420709999999</v>
+        <v>-25.27245538400001</v>
       </c>
       <c r="P27">
-        <v>-70.85309789999997</v>
+        <v>-89.60234181600003</v>
       </c>
       <c r="Q27">
-        <v>67.34690210000002</v>
+        <v>48.59765818399995</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09482413822153454</v>
+        <v>0.09548662657587961</v>
       </c>
       <c r="T27">
-        <v>1.132197187564308</v>
+        <v>1.147497149558421</v>
       </c>
       <c r="U27">
         <v>0.1186</v>
       </c>
       <c r="V27">
-        <v>0.1867449383925333</v>
+        <v>0.1795624407620512</v>
       </c>
       <c r="W27">
-        <v>0.09645205030664555</v>
+        <v>0.09730389452562073</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.8488406290569697</v>
+        <v>0.8161929125547784</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3803,22 +3803,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09595911624281231</v>
+        <v>0.1196182262791597</v>
       </c>
       <c r="C28">
-        <v>10374.75938074587</v>
+        <v>5374.872186956251</v>
       </c>
       <c r="D28">
-        <v>14967.66138074587</v>
+        <v>10170.45118695625</v>
       </c>
       <c r="E28">
-        <v>4821.001999999999</v>
+        <v>5023.678999999999</v>
       </c>
       <c r="F28">
-        <v>5269.602</v>
+        <v>5472.279</v>
       </c>
       <c r="G28">
         <v>676.7</v>
@@ -3839,45 +3839,45 @@
         <v>510.1</v>
       </c>
       <c r="M28">
-        <v>624.9747972</v>
+        <v>1098.8336232</v>
       </c>
       <c r="N28">
-        <v>-114.8747972</v>
+        <v>-588.7336232</v>
       </c>
       <c r="O28">
-        <v>-25.27245538400001</v>
+        <v>-129.521397104</v>
       </c>
       <c r="P28">
-        <v>-89.60234181600003</v>
+        <v>-459.212226096</v>
       </c>
       <c r="Q28">
-        <v>48.59765818399995</v>
+        <v>-321.012226096</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09548662657587961</v>
+        <v>0.0971770050719155</v>
       </c>
       <c r="T28">
-        <v>1.147497149558421</v>
+        <v>1.186535913901051</v>
       </c>
       <c r="U28">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V28">
-        <v>0.1795624407620512</v>
+        <v>0.1021282909720122</v>
       </c>
       <c r="W28">
-        <v>0.09730389452562073</v>
+        <v>0.18029263917282</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y28">
-        <v>0.8161929125547784</v>
+        <v>0.4642195044182371</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3885,22 +3885,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1196182262791597</v>
+        <v>0.1211682262791597</v>
       </c>
       <c r="C29">
-        <v>5374.872186956251</v>
+        <v>4963.032783672505</v>
       </c>
       <c r="D29">
-        <v>10170.45118695625</v>
+        <v>9961.288783672504</v>
       </c>
       <c r="E29">
-        <v>5023.678999999999</v>
+        <v>5226.356</v>
       </c>
       <c r="F29">
-        <v>5472.279</v>
+        <v>5674.956</v>
       </c>
       <c r="G29">
         <v>676.7</v>
@@ -3921,37 +3921,37 @@
         <v>510.1</v>
       </c>
       <c r="M29">
-        <v>1098.8336232</v>
+        <v>1139.5311648</v>
       </c>
       <c r="N29">
-        <v>-588.7336232</v>
+        <v>-629.4311648000003</v>
       </c>
       <c r="O29">
-        <v>-129.521397104</v>
+        <v>-138.4748562560001</v>
       </c>
       <c r="P29">
-        <v>-459.212226096</v>
+        <v>-490.9563085440002</v>
       </c>
       <c r="Q29">
-        <v>-321.012226096</v>
+        <v>-352.7563085440002</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.0971770050719155</v>
+        <v>0.09789057458680321</v>
       </c>
       <c r="T29">
-        <v>1.186535913901051</v>
+        <v>1.203015579371899</v>
       </c>
       <c r="U29">
         <v>0.2008</v>
       </c>
       <c r="V29">
-        <v>0.1021282909720122</v>
+        <v>0.09848085200872601</v>
       </c>
       <c r="W29">
-        <v>0.18029263917282</v>
+        <v>0.1810250449166478</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.4642195044182371</v>
+        <v>0.4476402364033</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3967,22 +3967,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1211682262791597</v>
+        <v>0.1227182262791597</v>
       </c>
       <c r="C30">
-        <v>4963.032783672505</v>
+        <v>4559.623156809059</v>
       </c>
       <c r="D30">
-        <v>9961.288783672504</v>
+        <v>9760.556156809058</v>
       </c>
       <c r="E30">
-        <v>5226.356</v>
+        <v>5429.032999999999</v>
       </c>
       <c r="F30">
-        <v>5674.956</v>
+        <v>5877.633</v>
       </c>
       <c r="G30">
         <v>676.7</v>
@@ -4003,37 +4003,37 @@
         <v>510.1</v>
       </c>
       <c r="M30">
-        <v>1139.5311648</v>
+        <v>1180.2287064</v>
       </c>
       <c r="N30">
-        <v>-629.4311648000003</v>
+        <v>-670.1287064000001</v>
       </c>
       <c r="O30">
-        <v>-138.4748562560001</v>
+        <v>-147.428315408</v>
       </c>
       <c r="P30">
-        <v>-490.9563085440002</v>
+        <v>-522.7003909920001</v>
       </c>
       <c r="Q30">
-        <v>-352.7563085440002</v>
+        <v>-384.5003909920001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09789057458680321</v>
+        <v>0.09862424465140607</v>
       </c>
       <c r="T30">
-        <v>1.203015579371899</v>
+        <v>1.219959460771503</v>
       </c>
       <c r="U30">
         <v>0.2008</v>
       </c>
       <c r="V30">
-        <v>0.09848085200872601</v>
+        <v>0.09508496056014927</v>
       </c>
       <c r="W30">
-        <v>0.1810250449166478</v>
+        <v>0.181706939919522</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.4476402364033</v>
+        <v>0.4322043661824967</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4049,22 +4049,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1227182262791597</v>
+        <v>0.1242682262791597</v>
       </c>
       <c r="C31">
-        <v>4559.623156809065</v>
+        <v>4164.14376072544</v>
       </c>
       <c r="D31">
-        <v>9760.556156809063</v>
+        <v>9567.753760725438</v>
       </c>
       <c r="E31">
-        <v>5429.032999999999</v>
+        <v>5631.709999999998</v>
       </c>
       <c r="F31">
-        <v>5877.632999999999</v>
+        <v>6080.309999999999</v>
       </c>
       <c r="G31">
         <v>676.7</v>
@@ -4085,37 +4085,37 @@
         <v>510.1</v>
       </c>
       <c r="M31">
-        <v>1180.2287064</v>
+        <v>1220.926248</v>
       </c>
       <c r="N31">
-        <v>-670.1287063999998</v>
+        <v>-710.8262479999999</v>
       </c>
       <c r="O31">
-        <v>-147.428315408</v>
+        <v>-156.38177456</v>
       </c>
       <c r="P31">
-        <v>-522.7003909919998</v>
+        <v>-554.4444734399999</v>
       </c>
       <c r="Q31">
-        <v>-384.5003909919998</v>
+        <v>-416.2444734399999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09862424465140607</v>
+        <v>0.09937887671785472</v>
       </c>
       <c r="T31">
-        <v>1.219959460771503</v>
+        <v>1.237387453068239</v>
       </c>
       <c r="U31">
         <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.0950849605601493</v>
+        <v>0.09191546187481098</v>
       </c>
       <c r="W31">
-        <v>0.181706939919522</v>
+        <v>0.182343375255538</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.4322043661824967</v>
+        <v>0.4177975539764135</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4131,22 +4131,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1242682262791597</v>
+        <v>0.1258182262791597</v>
       </c>
       <c r="C32">
-        <v>4164.14376072544</v>
+        <v>3776.133755749959</v>
       </c>
       <c r="D32">
-        <v>9567.753760725438</v>
+        <v>9382.420755749958</v>
       </c>
       <c r="E32">
-        <v>5631.709999999998</v>
+        <v>5834.386999999999</v>
       </c>
       <c r="F32">
-        <v>6080.309999999999</v>
+        <v>6282.986999999999</v>
       </c>
       <c r="G32">
         <v>676.7</v>
@@ -4167,37 +4167,37 @@
         <v>510.1</v>
       </c>
       <c r="M32">
-        <v>1220.926248</v>
+        <v>1261.6237896</v>
       </c>
       <c r="N32">
-        <v>-710.8262479999999</v>
+        <v>-751.5237895999999</v>
       </c>
       <c r="O32">
-        <v>-156.38177456</v>
+        <v>-165.335233712</v>
       </c>
       <c r="P32">
-        <v>-554.4444734399999</v>
+        <v>-586.1885558879999</v>
       </c>
       <c r="Q32">
-        <v>-416.2444734399999</v>
+        <v>-447.9885558879999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09937887671785472</v>
+        <v>0.1001553821775338</v>
       </c>
       <c r="T32">
-        <v>1.237387453068239</v>
+        <v>1.255320604561981</v>
       </c>
       <c r="U32">
         <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.09191546187481098</v>
+        <v>0.08895044697562353</v>
       </c>
       <c r="W32">
-        <v>0.182343375255538</v>
+        <v>0.1829387502472948</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.4177975539764135</v>
+        <v>0.4043202135255615</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1258182262791597</v>
+        <v>0.1273682262791597</v>
       </c>
       <c r="C33">
-        <v>3776.133755749959</v>
+        <v>3395.167330629432</v>
       </c>
       <c r="D33">
-        <v>9382.420755749958</v>
+        <v>9204.131330629431</v>
       </c>
       <c r="E33">
-        <v>5834.386999999999</v>
+        <v>6037.063999999998</v>
       </c>
       <c r="F33">
-        <v>6282.986999999999</v>
+        <v>6485.663999999999</v>
       </c>
       <c r="G33">
         <v>676.7</v>
@@ -4249,37 +4249,37 @@
         <v>510.1</v>
       </c>
       <c r="M33">
-        <v>1261.6237896</v>
+        <v>1302.3213312</v>
       </c>
       <c r="N33">
-        <v>-751.5237895999999</v>
+        <v>-792.2213311999999</v>
       </c>
       <c r="O33">
-        <v>-165.335233712</v>
+        <v>-174.288692864</v>
       </c>
       <c r="P33">
-        <v>-586.1885558879999</v>
+        <v>-617.9326383359999</v>
       </c>
       <c r="Q33">
-        <v>-447.9885558879999</v>
+        <v>-479.7326383359999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1001553821775338</v>
+        <v>0.1009547260330858</v>
       </c>
       <c r="T33">
-        <v>1.255320604561981</v>
+        <v>1.273781201687893</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.08895044697562353</v>
+        <v>0.08617074550763529</v>
       </c>
       <c r="W33">
-        <v>0.1829387502472948</v>
+        <v>0.1834969143020669</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.4043202135255615</v>
+        <v>0.3916852068528877</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4295,22 +4295,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1273682262791597</v>
+        <v>0.1289182262791597</v>
       </c>
       <c r="C34">
-        <v>3395.167330629432</v>
+        <v>3020.850436455549</v>
       </c>
       <c r="D34">
-        <v>9204.131330629431</v>
+        <v>9032.491436455548</v>
       </c>
       <c r="E34">
-        <v>6037.063999999998</v>
+        <v>6239.740999999999</v>
       </c>
       <c r="F34">
-        <v>6485.663999999999</v>
+        <v>6688.340999999999</v>
       </c>
       <c r="G34">
         <v>676.7</v>
@@ -4331,37 +4331,37 @@
         <v>510.1</v>
       </c>
       <c r="M34">
-        <v>1302.3213312</v>
+        <v>1343.0188728</v>
       </c>
       <c r="N34">
-        <v>-792.2213311999999</v>
+        <v>-832.9188727999999</v>
       </c>
       <c r="O34">
-        <v>-174.288692864</v>
+        <v>-183.242152016</v>
       </c>
       <c r="P34">
-        <v>-617.9326383359999</v>
+        <v>-649.6767207839999</v>
       </c>
       <c r="Q34">
-        <v>-479.7326383359999</v>
+        <v>-511.476720784</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1009547260330858</v>
+        <v>0.1017779308992512</v>
       </c>
       <c r="T34">
-        <v>1.273781201687893</v>
+        <v>1.292792861414578</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.08617074550763529</v>
+        <v>0.0835595107952827</v>
       </c>
       <c r="W34">
-        <v>0.1834969143020669</v>
+        <v>0.1840212502323073</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.3916852068528877</v>
+        <v>0.3798159581603758</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4377,22 +4377,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1289182262791597</v>
+        <v>0.1304682262791597</v>
       </c>
       <c r="C35">
-        <v>3020.850436455549</v>
+        <v>2652.817879338462</v>
       </c>
       <c r="D35">
-        <v>9032.491436455548</v>
+        <v>8867.135879338461</v>
       </c>
       <c r="E35">
-        <v>6239.740999999999</v>
+        <v>6442.417999999999</v>
       </c>
       <c r="F35">
-        <v>6688.340999999999</v>
+        <v>6891.017999999999</v>
       </c>
       <c r="G35">
         <v>676.7</v>
@@ -4413,37 +4413,37 @@
         <v>510.1</v>
       </c>
       <c r="M35">
-        <v>1343.0188728</v>
+        <v>1383.7164144</v>
       </c>
       <c r="N35">
-        <v>-832.9188727999999</v>
+        <v>-873.6164143999999</v>
       </c>
       <c r="O35">
-        <v>-183.242152016</v>
+        <v>-192.195611168</v>
       </c>
       <c r="P35">
-        <v>-649.6767207839999</v>
+        <v>-681.4208032319999</v>
       </c>
       <c r="Q35">
-        <v>-511.476720784</v>
+        <v>-543.220803232</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1017779308992512</v>
+        <v>0.1026260813674217</v>
       </c>
       <c r="T35">
-        <v>1.292792861414578</v>
+        <v>1.312380632042071</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.0835595107952827</v>
+        <v>0.0811018781248332</v>
       </c>
       <c r="W35">
-        <v>0.1840212502323073</v>
+        <v>0.1845147428725335</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3798159581603758</v>
+        <v>0.3686449005674236</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4459,22 +4459,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1304682262791597</v>
+        <v>0.1320182262791597</v>
       </c>
       <c r="C36">
-        <v>2652.817879338462</v>
+        <v>2290.730726681486</v>
       </c>
       <c r="D36">
-        <v>8867.135879338461</v>
+        <v>8707.725726681485</v>
       </c>
       <c r="E36">
-        <v>6442.417999999999</v>
+        <v>6645.094999999999</v>
       </c>
       <c r="F36">
-        <v>6891.017999999999</v>
+        <v>7093.695</v>
       </c>
       <c r="G36">
         <v>676.7</v>
@@ -4495,37 +4495,37 @@
         <v>510.1</v>
       </c>
       <c r="M36">
-        <v>1383.7164144</v>
+        <v>1424.413956</v>
       </c>
       <c r="N36">
-        <v>-873.6164143999999</v>
+        <v>-914.3139560000002</v>
       </c>
       <c r="O36">
-        <v>-192.195611168</v>
+        <v>-201.14907032</v>
       </c>
       <c r="P36">
-        <v>-681.4208032319999</v>
+        <v>-713.1648856800001</v>
       </c>
       <c r="Q36">
-        <v>-543.220803232</v>
+        <v>-574.9648856800002</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1026260813674217</v>
+        <v>0.1035003287730743</v>
       </c>
       <c r="T36">
-        <v>1.312380632042071</v>
+        <v>1.332571103304257</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.0811018781248332</v>
+        <v>0.07878468160698082</v>
       </c>
       <c r="W36">
-        <v>0.1845147428725335</v>
+        <v>0.1849800359333182</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3686449005674236</v>
+        <v>0.3581121891226401</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4541,22 +4541,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1320182262791597</v>
+        <v>0.1335682262791597</v>
       </c>
       <c r="C37">
-        <v>2290.730726681486</v>
+        <v>1934.273988289293</v>
       </c>
       <c r="D37">
-        <v>8707.725726681485</v>
+        <v>8553.945988289292</v>
       </c>
       <c r="E37">
-        <v>6645.094999999999</v>
+        <v>6847.771999999999</v>
       </c>
       <c r="F37">
-        <v>7093.695</v>
+        <v>7296.371999999999</v>
       </c>
       <c r="G37">
         <v>676.7</v>
@@ -4577,37 +4577,37 @@
         <v>510.1</v>
       </c>
       <c r="M37">
-        <v>1424.413956</v>
+        <v>1465.1114976</v>
       </c>
       <c r="N37">
-        <v>-914.3139560000002</v>
+        <v>-955.0114976</v>
       </c>
       <c r="O37">
-        <v>-201.14907032</v>
+        <v>-210.102529472</v>
       </c>
       <c r="P37">
-        <v>-713.1648856800001</v>
+        <v>-744.908968128</v>
       </c>
       <c r="Q37">
-        <v>-574.9648856800002</v>
+        <v>-606.7089681279999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1035003287730743</v>
+        <v>0.1044018964101536</v>
       </c>
       <c r="T37">
-        <v>1.332571103304257</v>
+        <v>1.353392526793386</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.07878468160698082</v>
+        <v>0.07659621822900914</v>
       </c>
       <c r="W37">
-        <v>0.1849800359333182</v>
+        <v>0.1854194793796149</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3581121891226401</v>
+        <v>0.3481646283136779</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4623,22 +4623,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1335682262791597</v>
+        <v>0.1351182262791597</v>
       </c>
       <c r="C38">
-        <v>1934.27398828929</v>
+        <v>1583.154538923924</v>
       </c>
       <c r="D38">
-        <v>8553.945988289288</v>
+        <v>8405.503538923922</v>
       </c>
       <c r="E38">
-        <v>6847.771999999998</v>
+        <v>7050.448999999999</v>
       </c>
       <c r="F38">
-        <v>7296.371999999998</v>
+        <v>7499.048999999999</v>
       </c>
       <c r="G38">
         <v>676.7</v>
@@ -4659,37 +4659,37 @@
         <v>510.1</v>
       </c>
       <c r="M38">
-        <v>1465.1114976</v>
+        <v>1505.8090392</v>
       </c>
       <c r="N38">
-        <v>-955.0114975999998</v>
+        <v>-995.7090392</v>
       </c>
       <c r="O38">
-        <v>-210.102529472</v>
+        <v>-219.055988624</v>
       </c>
       <c r="P38">
-        <v>-744.9089681279997</v>
+        <v>-776.6530505759999</v>
       </c>
       <c r="Q38">
-        <v>-606.7089681279997</v>
+        <v>-638.4530505759999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1044018964101536</v>
+        <v>0.1053320852420608</v>
       </c>
       <c r="T38">
-        <v>1.353392526793386</v>
+        <v>1.374874947853598</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.07659621822900915</v>
+        <v>0.07452605016876565</v>
       </c>
       <c r="W38">
-        <v>0.1854194793796149</v>
+        <v>0.1858351691261119</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3481646283136779</v>
+        <v>0.3387547734943893</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4705,22 +4705,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1351182262791597</v>
+        <v>0.1366682262791597</v>
       </c>
       <c r="C39">
-        <v>1583.154538923924</v>
+        <v>1237.099253478949</v>
       </c>
       <c r="D39">
-        <v>8405.503538923922</v>
+        <v>8262.125253478947</v>
       </c>
       <c r="E39">
-        <v>7050.448999999999</v>
+        <v>7253.125999999998</v>
       </c>
       <c r="F39">
-        <v>7499.048999999999</v>
+        <v>7701.725999999999</v>
       </c>
       <c r="G39">
         <v>676.7</v>
@@ -4741,37 +4741,37 @@
         <v>510.1</v>
       </c>
       <c r="M39">
-        <v>1505.8090392</v>
+        <v>1546.5065808</v>
       </c>
       <c r="N39">
-        <v>-995.7090392</v>
+        <v>-1036.4065808</v>
       </c>
       <c r="O39">
-        <v>-219.055988624</v>
+        <v>-228.0094477759999</v>
       </c>
       <c r="P39">
-        <v>-776.6530505759999</v>
+        <v>-808.3971330239999</v>
       </c>
       <c r="Q39">
-        <v>-638.4530505759999</v>
+        <v>-670.1971330239999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1053320852420608</v>
+        <v>0.1062922801653199</v>
       </c>
       <c r="T39">
-        <v>1.374874947853598</v>
+        <v>1.397050350238334</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.07452605016876565</v>
+        <v>0.07256483832221919</v>
       </c>
       <c r="W39">
-        <v>0.1858351691261119</v>
+        <v>0.1862289804648984</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3387547734943893</v>
+        <v>0.3298401741919054</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4787,22 +4787,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1366682262791597</v>
+        <v>0.1382182262791597</v>
       </c>
       <c r="C40">
-        <v>1237.099253478949</v>
+        <v>895.8533298100456</v>
       </c>
       <c r="D40">
-        <v>8262.125253478947</v>
+        <v>8123.556329810044</v>
       </c>
       <c r="E40">
-        <v>7253.125999999998</v>
+        <v>7455.802999999999</v>
       </c>
       <c r="F40">
-        <v>7701.725999999999</v>
+        <v>7904.402999999999</v>
       </c>
       <c r="G40">
         <v>676.7</v>
@@ -4823,37 +4823,37 @@
         <v>510.1</v>
       </c>
       <c r="M40">
-        <v>1546.5065808</v>
+        <v>1587.2041224</v>
       </c>
       <c r="N40">
-        <v>-1036.4065808</v>
+        <v>-1077.1041224</v>
       </c>
       <c r="O40">
-        <v>-228.0094477759999</v>
+        <v>-236.962906928</v>
       </c>
       <c r="P40">
-        <v>-808.3971330239999</v>
+        <v>-840.141215472</v>
       </c>
       <c r="Q40">
-        <v>-670.1971330239999</v>
+        <v>-701.9412154720001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1062922801653199</v>
+        <v>0.1072839568893415</v>
       </c>
       <c r="T40">
-        <v>1.397050350238334</v>
+        <v>1.419952814996339</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.07256483832221919</v>
+        <v>0.07070420144216227</v>
       </c>
       <c r="W40">
-        <v>0.1862289804648984</v>
+        <v>0.1866025963504138</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3298401741919054</v>
+        <v>0.3213827338280103</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4869,22 +4869,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1382182262791597</v>
+        <v>0.1397682262791597</v>
       </c>
       <c r="C41">
-        <v>895.8533298100456</v>
+        <v>559.1787775544681</v>
       </c>
       <c r="D41">
-        <v>8123.556329810044</v>
+        <v>7989.558777554467</v>
       </c>
       <c r="E41">
-        <v>7455.802999999999</v>
+        <v>7658.479999999999</v>
       </c>
       <c r="F41">
-        <v>7904.402999999999</v>
+        <v>8107.079999999999</v>
       </c>
       <c r="G41">
         <v>676.7</v>
@@ -4905,37 +4905,37 @@
         <v>510.1</v>
       </c>
       <c r="M41">
-        <v>1587.2041224</v>
+        <v>1627.901664</v>
       </c>
       <c r="N41">
-        <v>-1077.1041224</v>
+        <v>-1117.801664</v>
       </c>
       <c r="O41">
-        <v>-236.962906928</v>
+        <v>-245.91636608</v>
       </c>
       <c r="P41">
-        <v>-840.141215472</v>
+        <v>-871.8852979199999</v>
       </c>
       <c r="Q41">
-        <v>-701.9412154720001</v>
+        <v>-733.6852979199998</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1072839568893415</v>
+        <v>0.1083086895041639</v>
       </c>
       <c r="T41">
-        <v>1.419952814996339</v>
+        <v>1.443618695246278</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.07070420144216227</v>
+        <v>0.06893659640610823</v>
       </c>
       <c r="W41">
-        <v>0.1866025963504138</v>
+        <v>0.1869575314416535</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3213827338280103</v>
+        <v>0.3133481654823101</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4951,22 +4951,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1397682262791597</v>
+        <v>0.1413182262791597</v>
       </c>
       <c r="C42">
-        <v>559.1787775544681</v>
+        <v>226.8530540844895</v>
       </c>
       <c r="D42">
-        <v>7989.558777554467</v>
+        <v>7859.910054084489</v>
       </c>
       <c r="E42">
-        <v>7658.479999999999</v>
+        <v>7861.156999999999</v>
       </c>
       <c r="F42">
-        <v>8107.079999999999</v>
+        <v>8309.757</v>
       </c>
       <c r="G42">
         <v>676.7</v>
@@ -4987,37 +4987,37 @@
         <v>510.1</v>
       </c>
       <c r="M42">
-        <v>1627.901664</v>
+        <v>1668.5992056</v>
       </c>
       <c r="N42">
-        <v>-1117.801664</v>
+        <v>-1158.4992056</v>
       </c>
       <c r="O42">
-        <v>-245.91636608</v>
+        <v>-254.869825232</v>
       </c>
       <c r="P42">
-        <v>-871.8852979199999</v>
+        <v>-903.6293803680001</v>
       </c>
       <c r="Q42">
-        <v>-733.6852979199998</v>
+        <v>-765.429380368</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1083086895041639</v>
+        <v>0.1093681588177937</v>
       </c>
       <c r="T42">
-        <v>1.443618695246278</v>
+        <v>1.468086808725029</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.06893659640610823</v>
+        <v>0.06725521600595924</v>
       </c>
       <c r="W42">
-        <v>0.1869575314416535</v>
+        <v>0.1872951526260034</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3133481654823101</v>
+        <v>0.3057055272998147</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5033,22 +5033,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1413182262791597</v>
+        <v>0.1428682262791597</v>
       </c>
       <c r="C43">
-        <v>226.8530540844895</v>
+        <v>-101.3321688513442</v>
       </c>
       <c r="D43">
-        <v>7859.910054084489</v>
+        <v>7734.401831148655</v>
       </c>
       <c r="E43">
-        <v>7861.156999999999</v>
+        <v>8063.833999999999</v>
       </c>
       <c r="F43">
-        <v>8309.757</v>
+        <v>8512.433999999999</v>
       </c>
       <c r="G43">
         <v>676.7</v>
@@ -5069,37 +5069,37 @@
         <v>510.1</v>
       </c>
       <c r="M43">
-        <v>1668.5992056</v>
+        <v>1709.2967472</v>
       </c>
       <c r="N43">
-        <v>-1158.4992056</v>
+        <v>-1199.1967472</v>
       </c>
       <c r="O43">
-        <v>-254.869825232</v>
+        <v>-263.823284384</v>
       </c>
       <c r="P43">
-        <v>-903.6293803680001</v>
+        <v>-935.3734628159999</v>
       </c>
       <c r="Q43">
-        <v>-765.429380368</v>
+        <v>-797.173462816</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1093681588177937</v>
+        <v>0.1104641615560316</v>
       </c>
       <c r="T43">
-        <v>1.468086808725029</v>
+        <v>1.493398650254771</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.06725521600595924</v>
+        <v>0.06565390133915069</v>
       </c>
       <c r="W43">
-        <v>0.1872951526260034</v>
+        <v>0.1876166966110985</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3057055272998147</v>
+        <v>0.2984268242688668</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5115,22 +5115,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1428682262791597</v>
+        <v>0.1444182262791597</v>
       </c>
       <c r="C44">
-        <v>-101.3321688513442</v>
+        <v>-425.5721221774875</v>
       </c>
       <c r="D44">
-        <v>7734.401831148655</v>
+        <v>7612.838877822512</v>
       </c>
       <c r="E44">
-        <v>8063.833999999999</v>
+        <v>8266.510999999999</v>
       </c>
       <c r="F44">
-        <v>8512.433999999999</v>
+        <v>8715.110999999999</v>
       </c>
       <c r="G44">
         <v>676.7</v>
@@ -5151,37 +5151,37 @@
         <v>510.1</v>
       </c>
       <c r="M44">
-        <v>1709.2967472</v>
+        <v>1749.9942888</v>
       </c>
       <c r="N44">
-        <v>-1199.1967472</v>
+        <v>-1239.8942888</v>
       </c>
       <c r="O44">
-        <v>-263.823284384</v>
+        <v>-272.776743536</v>
       </c>
       <c r="P44">
-        <v>-935.3734628159999</v>
+        <v>-967.117545264</v>
       </c>
       <c r="Q44">
-        <v>-797.173462816</v>
+        <v>-828.917545264</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1104641615560316</v>
+        <v>0.1115986205306988</v>
       </c>
       <c r="T44">
-        <v>1.49339865025477</v>
+        <v>1.51959862657503</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.06565390133915069</v>
+        <v>0.06412706642428671</v>
       </c>
       <c r="W44">
-        <v>0.1876166966110985</v>
+        <v>0.1879232850620032</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5189,7 +5189,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2984268242688668</v>
+        <v>0.2914866655649396</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5197,22 +5197,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1444182262791597</v>
+        <v>0.1459682262791597</v>
       </c>
       <c r="C45">
-        <v>-425.5721221774875</v>
+        <v>-746.0499528295131</v>
       </c>
       <c r="D45">
-        <v>7612.838877822512</v>
+        <v>7495.038047170486</v>
       </c>
       <c r="E45">
-        <v>8266.510999999999</v>
+        <v>8469.187999999998</v>
       </c>
       <c r="F45">
-        <v>8715.110999999999</v>
+        <v>8917.787999999999</v>
       </c>
       <c r="G45">
         <v>676.7</v>
@@ -5233,37 +5233,37 @@
         <v>510.1</v>
       </c>
       <c r="M45">
-        <v>1749.9942888</v>
+        <v>1790.6918304</v>
       </c>
       <c r="N45">
-        <v>-1239.8942888</v>
+        <v>-1280.5918304</v>
       </c>
       <c r="O45">
-        <v>-272.776743536</v>
+        <v>-281.730202688</v>
       </c>
       <c r="P45">
-        <v>-967.117545264</v>
+        <v>-998.861627712</v>
       </c>
       <c r="Q45">
-        <v>-828.917545264</v>
+        <v>-860.6616277119999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1115986205306988</v>
+        <v>0.1127735958973184</v>
       </c>
       <c r="T45">
-        <v>1.51959862657503</v>
+        <v>1.546734316335298</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.06412706642428671</v>
+        <v>0.06266963309646202</v>
       </c>
       <c r="W45">
-        <v>0.1879232850620032</v>
+        <v>0.1882159376742304</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2914866655649396</v>
+        <v>0.2848619686202819</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1459682262791597</v>
+        <v>0.1475182262791597</v>
       </c>
       <c r="C46">
-        <v>-746.0499528295131</v>
+        <v>-1062.937644443728</v>
       </c>
       <c r="D46">
-        <v>7495.038047170486</v>
+        <v>7380.827355556271</v>
       </c>
       <c r="E46">
-        <v>8469.187999999998</v>
+        <v>8671.864999999998</v>
       </c>
       <c r="F46">
-        <v>8917.787999999999</v>
+        <v>9120.464999999998</v>
       </c>
       <c r="G46">
         <v>676.7</v>
@@ -5315,37 +5315,37 @@
         <v>510.1</v>
       </c>
       <c r="M46">
-        <v>1790.6918304</v>
+        <v>1831.389372</v>
       </c>
       <c r="N46">
-        <v>-1280.5918304</v>
+        <v>-1321.289372</v>
       </c>
       <c r="O46">
-        <v>-281.730202688</v>
+        <v>-290.68366184</v>
       </c>
       <c r="P46">
-        <v>-998.861627712</v>
+        <v>-1030.60571016</v>
       </c>
       <c r="Q46">
-        <v>-860.6616277119999</v>
+        <v>-892.4057101599997</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1127735958973184</v>
+        <v>0.113991297640906</v>
       </c>
       <c r="T46">
-        <v>1.546734316335298</v>
+        <v>1.574856758450485</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.06266963309646202</v>
+        <v>0.06127697458320731</v>
       </c>
       <c r="W46">
-        <v>0.1882159376742304</v>
+        <v>0.188495583503692</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2848619686202819</v>
+        <v>0.2785317026509423</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5361,22 +5361,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1475182262791597</v>
+        <v>0.1490682262791597</v>
       </c>
       <c r="C47">
-        <v>-1062.937644443728</v>
+        <v>-1376.396855132489</v>
       </c>
       <c r="D47">
-        <v>7380.827355556271</v>
+        <v>7270.045144867511</v>
       </c>
       <c r="E47">
-        <v>8671.864999999998</v>
+        <v>8874.541999999999</v>
       </c>
       <c r="F47">
-        <v>9120.464999999998</v>
+        <v>9323.142</v>
       </c>
       <c r="G47">
         <v>676.7</v>
@@ -5397,37 +5397,37 @@
         <v>510.1</v>
       </c>
       <c r="M47">
-        <v>1831.389372</v>
+        <v>1872.0869136</v>
       </c>
       <c r="N47">
-        <v>-1321.289372</v>
+        <v>-1361.9869136</v>
       </c>
       <c r="O47">
-        <v>-290.68366184</v>
+        <v>-299.6371209920001</v>
       </c>
       <c r="P47">
-        <v>-1030.60571016</v>
+        <v>-1062.349792608</v>
       </c>
       <c r="Q47">
-        <v>-892.4057101599997</v>
+        <v>-924.1497926080001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.113991297640906</v>
+        <v>0.1152540994490709</v>
       </c>
       <c r="T47">
-        <v>1.574856758450485</v>
+        <v>1.604020772495865</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.06127697458320731</v>
+        <v>0.0599448664400941</v>
       </c>
       <c r="W47">
-        <v>0.188495583503692</v>
+        <v>0.1887630708188291</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2785317026509423</v>
+        <v>0.2724766656367913</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5443,22 +5443,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1490682262791597</v>
+        <v>0.1506182262791597</v>
       </c>
       <c r="C48">
-        <v>-1376.396855132489</v>
+        <v>-1686.579680927834</v>
       </c>
       <c r="D48">
-        <v>7270.045144867511</v>
+        <v>7162.539319072165</v>
       </c>
       <c r="E48">
-        <v>8874.541999999999</v>
+        <v>9077.218999999999</v>
       </c>
       <c r="F48">
-        <v>9323.142</v>
+        <v>9525.819</v>
       </c>
       <c r="G48">
         <v>676.7</v>
@@ -5479,37 +5479,37 @@
         <v>510.1</v>
       </c>
       <c r="M48">
-        <v>1872.0869136</v>
+        <v>1912.7844552</v>
       </c>
       <c r="N48">
-        <v>-1361.9869136</v>
+        <v>-1402.6844552</v>
       </c>
       <c r="O48">
-        <v>-299.6371209920001</v>
+        <v>-308.590580144</v>
       </c>
       <c r="P48">
-        <v>-1062.349792608</v>
+        <v>-1094.093875056</v>
       </c>
       <c r="Q48">
-        <v>-924.1497926080001</v>
+        <v>-955.8938750559998</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1152540994490709</v>
+        <v>0.1165645541556572</v>
       </c>
       <c r="T48">
-        <v>1.604020772495865</v>
+        <v>1.634285315373145</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.0599448664400941</v>
+        <v>0.05866944374987934</v>
       </c>
       <c r="W48">
-        <v>0.1887630708188291</v>
+        <v>0.1890191756950242</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2724766656367913</v>
+        <v>0.2666792897721788</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5525,22 +5525,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1506182262791597</v>
+        <v>0.1521682262791597</v>
       </c>
       <c r="C49">
-        <v>-1686.579680927834</v>
+        <v>-1993.629352475684</v>
       </c>
       <c r="D49">
-        <v>7162.539319072165</v>
+        <v>7058.166647524316</v>
       </c>
       <c r="E49">
-        <v>9077.218999999999</v>
+        <v>9279.895999999999</v>
       </c>
       <c r="F49">
-        <v>9525.819</v>
+        <v>9728.495999999999</v>
       </c>
       <c r="G49">
         <v>676.7</v>
@@ -5561,37 +5561,37 @@
         <v>510.1</v>
       </c>
       <c r="M49">
-        <v>1912.7844552</v>
+        <v>1953.4819968</v>
       </c>
       <c r="N49">
-        <v>-1402.6844552</v>
+        <v>-1443.3819968</v>
       </c>
       <c r="O49">
-        <v>-308.590580144</v>
+        <v>-317.544039296</v>
       </c>
       <c r="P49">
-        <v>-1094.093875056</v>
+        <v>-1125.837957504</v>
       </c>
       <c r="Q49">
-        <v>-955.8938750559998</v>
+        <v>-987.637957504</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1165645541556572</v>
+        <v>0.1179254109663429</v>
       </c>
       <c r="T49">
-        <v>1.634285315373145</v>
+        <v>1.665713879130321</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.05866944374987934</v>
+        <v>0.05744716367175685</v>
       </c>
       <c r="W49">
-        <v>0.1890191756950242</v>
+        <v>0.1892646095347112</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2666792897721788</v>
+        <v>0.2611234712352584</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5607,22 +5607,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1521682262791597</v>
+        <v>0.1537182262791597</v>
       </c>
       <c r="C50">
-        <v>-1993.629352475679</v>
+        <v>-2297.680871691399</v>
       </c>
       <c r="D50">
-        <v>7058.166647524318</v>
+        <v>6956.7921283086</v>
       </c>
       <c r="E50">
-        <v>9279.895999999997</v>
+        <v>9482.572999999999</v>
       </c>
       <c r="F50">
-        <v>9728.495999999997</v>
+        <v>9931.172999999999</v>
       </c>
       <c r="G50">
         <v>676.7</v>
@@ -5643,37 +5643,37 @@
         <v>510.1</v>
       </c>
       <c r="M50">
-        <v>1953.481996799999</v>
+        <v>1994.1795384</v>
       </c>
       <c r="N50">
-        <v>-1443.3819968</v>
+        <v>-1484.0795384</v>
       </c>
       <c r="O50">
-        <v>-317.5440392959999</v>
+        <v>-326.497498448</v>
       </c>
       <c r="P50">
-        <v>-1125.837957504</v>
+        <v>-1157.582039952</v>
       </c>
       <c r="Q50">
-        <v>-987.6379575039996</v>
+        <v>-1019.382039952</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1179254109663429</v>
+        <v>0.119339634710781</v>
       </c>
       <c r="T50">
-        <v>1.665713879130321</v>
+        <v>1.698374935583857</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.05744716367175687</v>
+        <v>0.05627477257641487</v>
       </c>
       <c r="W50">
-        <v>0.1892646095347112</v>
+        <v>0.1895000256666559</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2611234712352585</v>
+        <v>0.2557944208018857</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5689,22 +5689,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1537182262791597</v>
+        <v>0.1552682262791597</v>
       </c>
       <c r="C51">
-        <v>-2297.680871691399</v>
+        <v>-2598.861594327591</v>
       </c>
       <c r="D51">
-        <v>6956.7921283086</v>
+        <v>6858.288405672408</v>
       </c>
       <c r="E51">
-        <v>9482.572999999999</v>
+        <v>9685.249999999998</v>
       </c>
       <c r="F51">
-        <v>9931.172999999999</v>
+        <v>10133.85</v>
       </c>
       <c r="G51">
         <v>676.7</v>
@@ -5725,37 +5725,37 @@
         <v>510.1</v>
       </c>
       <c r="M51">
-        <v>1994.1795384</v>
+        <v>2034.87708</v>
       </c>
       <c r="N51">
-        <v>-1484.0795384</v>
+        <v>-1524.77708</v>
       </c>
       <c r="O51">
-        <v>-326.497498448</v>
+        <v>-335.4509576</v>
       </c>
       <c r="P51">
-        <v>-1157.582039952</v>
+        <v>-1189.3261224</v>
       </c>
       <c r="Q51">
-        <v>-1019.382039952</v>
+        <v>-1051.1261224</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.119339634710781</v>
+        <v>0.1208104274049966</v>
       </c>
       <c r="T51">
-        <v>1.698374935583857</v>
+        <v>1.732342434295534</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.05627477257641487</v>
+        <v>0.05514927712488658</v>
       </c>
       <c r="W51">
-        <v>0.1895000256666559</v>
+        <v>0.1897260251533228</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2557944208018857</v>
+        <v>0.250678532385848</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5771,22 +5771,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1552682262791597</v>
+        <v>0.1568182262791597</v>
       </c>
       <c r="C52">
-        <v>-2598.861594327591</v>
+        <v>-2897.291763740167</v>
       </c>
       <c r="D52">
-        <v>6858.288405672408</v>
+        <v>6762.535236259831</v>
       </c>
       <c r="E52">
-        <v>9685.249999999998</v>
+        <v>9887.926999999998</v>
       </c>
       <c r="F52">
-        <v>10133.85</v>
+        <v>10336.527</v>
       </c>
       <c r="G52">
         <v>676.7</v>
@@ -5807,37 +5807,37 @@
         <v>510.1</v>
       </c>
       <c r="M52">
-        <v>2034.87708</v>
+        <v>2075.5746216</v>
       </c>
       <c r="N52">
-        <v>-1524.77708</v>
+        <v>-1565.4746216</v>
       </c>
       <c r="O52">
-        <v>-335.4509576</v>
+        <v>-344.404416752</v>
       </c>
       <c r="P52">
-        <v>-1189.3261224</v>
+        <v>-1221.070204848</v>
       </c>
       <c r="Q52">
-        <v>-1051.1261224</v>
+        <v>-1082.870204848</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1208104274049966</v>
+        <v>0.1223412524540782</v>
       </c>
       <c r="T52">
-        <v>1.732342434295534</v>
+        <v>1.767696361526055</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.05514927712488658</v>
+        <v>0.0540679187498888</v>
       </c>
       <c r="W52">
-        <v>0.1897260251533228</v>
+        <v>0.1899431619150223</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.250678532385848</v>
+        <v>0.2457632670449491</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5853,22 +5853,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1568182262791597</v>
+        <v>0.1583682262791597</v>
       </c>
       <c r="C53">
-        <v>-2897.291763740167</v>
+        <v>-3193.085000556484</v>
       </c>
       <c r="D53">
-        <v>6762.535236259831</v>
+        <v>6669.418999443516</v>
       </c>
       <c r="E53">
-        <v>9887.926999999998</v>
+        <v>10090.604</v>
       </c>
       <c r="F53">
-        <v>10336.527</v>
+        <v>10539.204</v>
       </c>
       <c r="G53">
         <v>676.7</v>
@@ -5889,37 +5889,37 @@
         <v>510.1</v>
       </c>
       <c r="M53">
-        <v>2075.5746216</v>
+        <v>2116.2721632</v>
       </c>
       <c r="N53">
-        <v>-1565.4746216</v>
+        <v>-1606.1721632</v>
       </c>
       <c r="O53">
-        <v>-344.404416752</v>
+        <v>-353.357875904</v>
       </c>
       <c r="P53">
-        <v>-1221.070204848</v>
+        <v>-1252.814287296</v>
       </c>
       <c r="Q53">
-        <v>-1082.870204848</v>
+        <v>-1114.614287296</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1223412524540782</v>
+        <v>0.1239358618802048</v>
       </c>
       <c r="T53">
-        <v>1.767696361526055</v>
+        <v>1.804523369057848</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.0540679187498888</v>
+        <v>0.05302815108162171</v>
       </c>
       <c r="W53">
-        <v>0.1899431619150223</v>
+        <v>0.1901519472628104</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2457632670449491</v>
+        <v>0.2410370503710078</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5935,22 +5935,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1583682262791597</v>
+        <v>0.1599182262791597</v>
       </c>
       <c r="C54">
-        <v>-3193.085000556484</v>
+        <v>-3486.348752438249</v>
       </c>
       <c r="D54">
-        <v>6669.418999443516</v>
+        <v>6578.832247561751</v>
       </c>
       <c r="E54">
-        <v>10090.604</v>
+        <v>10293.281</v>
       </c>
       <c r="F54">
-        <v>10539.204</v>
+        <v>10741.881</v>
       </c>
       <c r="G54">
         <v>676.7</v>
@@ -5971,37 +5971,37 @@
         <v>510.1</v>
       </c>
       <c r="M54">
-        <v>2116.2721632</v>
+        <v>2156.9697048</v>
       </c>
       <c r="N54">
-        <v>-1606.1721632</v>
+        <v>-1646.8697048</v>
       </c>
       <c r="O54">
-        <v>-353.357875904</v>
+        <v>-362.311335056</v>
       </c>
       <c r="P54">
-        <v>-1252.814287296</v>
+        <v>-1284.558369744</v>
       </c>
       <c r="Q54">
-        <v>-1114.614287296</v>
+        <v>-1146.358369744</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1239358618802048</v>
+        <v>0.1255983270265922</v>
       </c>
       <c r="T54">
-        <v>1.804523369057848</v>
+        <v>1.842917483293121</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.05302815108162171</v>
+        <v>0.05202761992913828</v>
       </c>
       <c r="W54">
-        <v>0.1901519472628104</v>
+        <v>0.190352853918229</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2410370503710078</v>
+        <v>0.2364891814960831</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6017,22 +6017,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1599182262791597</v>
+        <v>0.1614682262791597</v>
       </c>
       <c r="C55">
-        <v>-3486.348752438249</v>
+        <v>-3777.184707682453</v>
       </c>
       <c r="D55">
-        <v>6578.832247561751</v>
+        <v>6490.673292317546</v>
       </c>
       <c r="E55">
-        <v>10293.281</v>
+        <v>10495.958</v>
       </c>
       <c r="F55">
-        <v>10741.881</v>
+        <v>10944.558</v>
       </c>
       <c r="G55">
         <v>676.7</v>
@@ -6053,37 +6053,37 @@
         <v>510.1</v>
       </c>
       <c r="M55">
-        <v>2156.9697048</v>
+        <v>2197.6672464</v>
       </c>
       <c r="N55">
-        <v>-1646.8697048</v>
+        <v>-1687.5672464</v>
       </c>
       <c r="O55">
-        <v>-362.311335056</v>
+        <v>-371.264794208</v>
       </c>
       <c r="P55">
-        <v>-1284.558369744</v>
+        <v>-1316.302452192</v>
       </c>
       <c r="Q55">
-        <v>-1146.358369744</v>
+        <v>-1178.102452192</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1255983270265922</v>
+        <v>0.1273330732663007</v>
       </c>
       <c r="T55">
-        <v>1.842917483293121</v>
+        <v>1.882980906842972</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.05202761992913828</v>
+        <v>0.05106414548600609</v>
       </c>
       <c r="W55">
-        <v>0.190352853918229</v>
+        <v>0.19054631958641</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2364891814960831</v>
+        <v>0.2321097522091186</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6099,22 +6099,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1614682262791597</v>
+        <v>0.1630182262791597</v>
       </c>
       <c r="C56">
-        <v>-3777.184707682453</v>
+        <v>-4065.689176007493</v>
       </c>
       <c r="D56">
-        <v>6490.673292317546</v>
+        <v>6404.845823992506</v>
       </c>
       <c r="E56">
-        <v>10495.958</v>
+        <v>10698.635</v>
       </c>
       <c r="F56">
-        <v>10944.558</v>
+        <v>11147.235</v>
       </c>
       <c r="G56">
         <v>676.7</v>
@@ -6135,37 +6135,37 @@
         <v>510.1</v>
       </c>
       <c r="M56">
-        <v>2197.6672464</v>
+        <v>2238.364788</v>
       </c>
       <c r="N56">
-        <v>-1687.5672464</v>
+        <v>-1728.264788</v>
       </c>
       <c r="O56">
-        <v>-371.264794208</v>
+        <v>-380.21825336</v>
       </c>
       <c r="P56">
-        <v>-1316.302452192</v>
+        <v>-1348.04653464</v>
       </c>
       <c r="Q56">
-        <v>-1178.102452192</v>
+        <v>-1209.84653464</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1273330732663007</v>
+        <v>0.1291449193388851</v>
       </c>
       <c r="T56">
-        <v>1.882980906842972</v>
+        <v>1.924824926995038</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.05106414548600609</v>
+        <v>0.05013570647716962</v>
       </c>
       <c r="W56">
-        <v>0.19054631958641</v>
+        <v>0.1907327501393843</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2321097522091186</v>
+        <v>0.2278895748962255</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6181,22 +6181,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1630182262791597</v>
+        <v>0.1645682262791597</v>
       </c>
       <c r="C57">
-        <v>-4065.689176007493</v>
+        <v>-4351.953439522352</v>
       </c>
       <c r="D57">
-        <v>6404.845823992506</v>
+        <v>6321.258560477649</v>
       </c>
       <c r="E57">
-        <v>10698.635</v>
+        <v>10901.312</v>
       </c>
       <c r="F57">
-        <v>11147.235</v>
+        <v>11349.912</v>
       </c>
       <c r="G57">
         <v>676.7</v>
@@ -6217,37 +6217,37 @@
         <v>510.1</v>
       </c>
       <c r="M57">
-        <v>2238.364788</v>
+        <v>2279.0623296</v>
       </c>
       <c r="N57">
-        <v>-1728.264788</v>
+        <v>-1768.9623296</v>
       </c>
       <c r="O57">
-        <v>-380.21825336</v>
+        <v>-389.1717125120001</v>
       </c>
       <c r="P57">
-        <v>-1348.04653464</v>
+        <v>-1379.790617088</v>
       </c>
       <c r="Q57">
-        <v>-1209.84653464</v>
+        <v>-1241.590617088</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1291449193388851</v>
+        <v>0.1310391220511325</v>
       </c>
       <c r="T57">
-        <v>1.924824926995038</v>
+        <v>1.968570948063107</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.05013570647716962</v>
+        <v>0.04924042600436301</v>
       </c>
       <c r="W57">
-        <v>0.1907327501393843</v>
+        <v>0.1909125224583239</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6255,7 +6255,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2278895748962255</v>
+        <v>0.22382011820165</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6263,22 +6263,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1645682262791597</v>
+        <v>0.1661182262791597</v>
       </c>
       <c r="C58">
-        <v>-4351.953439522352</v>
+        <v>-4636.06407656756</v>
       </c>
       <c r="D58">
-        <v>6321.258560477649</v>
+        <v>6239.82492343244</v>
       </c>
       <c r="E58">
-        <v>10901.312</v>
+        <v>11103.989</v>
       </c>
       <c r="F58">
-        <v>11349.912</v>
+        <v>11552.589</v>
       </c>
       <c r="G58">
         <v>676.7</v>
@@ -6299,37 +6299,37 @@
         <v>510.1</v>
       </c>
       <c r="M58">
-        <v>2279.0623296</v>
+        <v>2319.7598712</v>
       </c>
       <c r="N58">
-        <v>-1768.9623296</v>
+        <v>-1809.6598712</v>
       </c>
       <c r="O58">
-        <v>-389.1717125120001</v>
+        <v>-398.125171664</v>
       </c>
       <c r="P58">
-        <v>-1379.790617088</v>
+        <v>-1411.534699536</v>
       </c>
       <c r="Q58">
-        <v>-1241.590617088</v>
+        <v>-1273.334699536</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1310391220511325</v>
+        <v>0.1330214272151124</v>
       </c>
       <c r="T58">
-        <v>1.968570948063107</v>
+        <v>2.014351667785505</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.04924042600436301</v>
+        <v>0.04837655888147946</v>
       </c>
       <c r="W58">
-        <v>0.1909125224583239</v>
+        <v>0.1910859869765989</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.22382011820165</v>
+        <v>0.2198934494612702</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1661182262791597</v>
+        <v>0.1676682262791597</v>
       </c>
       <c r="C59">
-        <v>-4636.06407656756</v>
+        <v>-4918.103260843267</v>
       </c>
       <c r="D59">
-        <v>6239.82492343244</v>
+        <v>6160.462739156733</v>
       </c>
       <c r="E59">
-        <v>11103.989</v>
+        <v>11306.666</v>
       </c>
       <c r="F59">
-        <v>11552.589</v>
+        <v>11755.266</v>
       </c>
       <c r="G59">
         <v>676.7</v>
@@ -6381,37 +6381,37 @@
         <v>510.1</v>
       </c>
       <c r="M59">
-        <v>2319.7598712</v>
+        <v>2360.4574128</v>
       </c>
       <c r="N59">
-        <v>-1809.6598712</v>
+        <v>-1850.3574128</v>
       </c>
       <c r="O59">
-        <v>-398.125171664</v>
+        <v>-407.078630816</v>
       </c>
       <c r="P59">
-        <v>-1411.534699536</v>
+        <v>-1443.278781984</v>
       </c>
       <c r="Q59">
-        <v>-1273.334699536</v>
+        <v>-1305.078781984</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1330214272151124</v>
+        <v>0.1350981278630912</v>
       </c>
       <c r="T59">
-        <v>2.014351667785505</v>
+        <v>2.062312421780398</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.04837655888147946</v>
+        <v>0.04754248028007464</v>
       </c>
       <c r="W59">
-        <v>0.1910859869765989</v>
+        <v>0.191253469959761</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2198934494612702</v>
+        <v>0.2161021830912483</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6427,22 +6427,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1676682262791597</v>
+        <v>0.1692182262791597</v>
       </c>
       <c r="C60">
-        <v>-4918.103260843265</v>
+        <v>-5198.14903799693</v>
       </c>
       <c r="D60">
-        <v>6160.462739156733</v>
+        <v>6083.093962003068</v>
       </c>
       <c r="E60">
-        <v>11306.666</v>
+        <v>11509.343</v>
       </c>
       <c r="F60">
-        <v>11755.266</v>
+        <v>11957.943</v>
       </c>
       <c r="G60">
         <v>676.7</v>
@@ -6463,37 +6463,37 @@
         <v>510.1</v>
       </c>
       <c r="M60">
-        <v>2360.457412799999</v>
+        <v>2401.154954399999</v>
       </c>
       <c r="N60">
-        <v>-1850.3574128</v>
+        <v>-1891.0549544</v>
       </c>
       <c r="O60">
-        <v>-407.0786308159999</v>
+        <v>-416.0320899679999</v>
       </c>
       <c r="P60">
-        <v>-1443.278781984</v>
+        <v>-1475.022864432</v>
       </c>
       <c r="Q60">
-        <v>-1305.078781984</v>
+        <v>-1336.822864432</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1350981278630912</v>
+        <v>0.1372761309817032</v>
       </c>
       <c r="T60">
-        <v>2.062312421780397</v>
+        <v>2.112612724750651</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.04754248028007465</v>
+        <v>0.0467366755295649</v>
       </c>
       <c r="W60">
-        <v>0.191253469959761</v>
+        <v>0.1914152755536634</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2161021830912484</v>
+        <v>0.212439434225295</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6509,22 +6509,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1692182262791597</v>
+        <v>0.1707682262791597</v>
       </c>
       <c r="C61">
-        <v>-5198.14903799693</v>
+        <v>-5476.275581627662</v>
       </c>
       <c r="D61">
-        <v>6083.093962003068</v>
+        <v>6007.644418372335</v>
       </c>
       <c r="E61">
-        <v>11509.343</v>
+        <v>11712.02</v>
       </c>
       <c r="F61">
-        <v>11957.943</v>
+        <v>12160.62</v>
       </c>
       <c r="G61">
         <v>676.7</v>
@@ -6545,37 +6545,37 @@
         <v>510.1</v>
       </c>
       <c r="M61">
-        <v>2401.154954399999</v>
+        <v>2441.852496</v>
       </c>
       <c r="N61">
-        <v>-1891.0549544</v>
+        <v>-1931.752496</v>
       </c>
       <c r="O61">
-        <v>-416.0320899679999</v>
+        <v>-424.9855491199999</v>
       </c>
       <c r="P61">
-        <v>-1475.022864432</v>
+        <v>-1506.76694688</v>
       </c>
       <c r="Q61">
-        <v>-1336.822864432</v>
+        <v>-1368.56694688</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1372761309817032</v>
+        <v>0.1395630342562458</v>
       </c>
       <c r="T61">
-        <v>2.112612724750651</v>
+        <v>2.165428042869417</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.0467366755295649</v>
+        <v>0.04595773093740549</v>
       </c>
       <c r="W61">
-        <v>0.1914152755536634</v>
+        <v>0.191571687627769</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.212439434225295</v>
+        <v>0.2088987769882068</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6591,22 +6591,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1707682262791597</v>
+        <v>0.1723182262791597</v>
       </c>
       <c r="C62">
-        <v>-5476.275581627662</v>
+        <v>-5752.553430472405</v>
       </c>
       <c r="D62">
-        <v>6007.644418372335</v>
+        <v>5934.043569527594</v>
       </c>
       <c r="E62">
-        <v>11712.02</v>
+        <v>11914.697</v>
       </c>
       <c r="F62">
-        <v>12160.62</v>
+        <v>12363.297</v>
       </c>
       <c r="G62">
         <v>676.7</v>
@@ -6627,37 +6627,37 @@
         <v>510.1</v>
       </c>
       <c r="M62">
-        <v>2441.852496</v>
+        <v>2482.5500376</v>
       </c>
       <c r="N62">
-        <v>-1931.752496</v>
+        <v>-1972.4500376</v>
       </c>
       <c r="O62">
-        <v>-424.9855491199999</v>
+        <v>-433.939008272</v>
       </c>
       <c r="P62">
-        <v>-1506.76694688</v>
+        <v>-1538.511029328</v>
       </c>
       <c r="Q62">
-        <v>-1368.56694688</v>
+        <v>-1400.311029328</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1395630342562458</v>
+        <v>0.1419672146217905</v>
       </c>
       <c r="T62">
-        <v>2.165428042869417</v>
+        <v>2.220951838840429</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.04595773093740549</v>
+        <v>0.04520432551220211</v>
       </c>
       <c r="W62">
-        <v>0.191571687627769</v>
+        <v>0.1917229714371498</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2088987769882068</v>
+        <v>0.2054742068736459</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6673,22 +6673,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1723182262791597</v>
+        <v>0.1738682262791597</v>
       </c>
       <c r="C63">
-        <v>-5752.553430472405</v>
+        <v>-6027.049708368225</v>
       </c>
       <c r="D63">
-        <v>5934.043569527594</v>
+        <v>5862.224291631774</v>
       </c>
       <c r="E63">
-        <v>11914.697</v>
+        <v>12117.374</v>
       </c>
       <c r="F63">
-        <v>12363.297</v>
+        <v>12565.974</v>
       </c>
       <c r="G63">
         <v>676.7</v>
@@ -6709,37 +6709,37 @@
         <v>510.1</v>
       </c>
       <c r="M63">
-        <v>2482.5500376</v>
+        <v>2523.2475792</v>
       </c>
       <c r="N63">
-        <v>-1972.4500376</v>
+        <v>-2013.1475792</v>
       </c>
       <c r="O63">
-        <v>-433.939008272</v>
+        <v>-442.8924674239999</v>
       </c>
       <c r="P63">
-        <v>-1538.511029328</v>
+        <v>-1570.255111776</v>
       </c>
       <c r="Q63">
-        <v>-1400.311029328</v>
+        <v>-1432.055111776</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1419672146217905</v>
+        <v>0.1444979307960482</v>
       </c>
       <c r="T63">
-        <v>2.220951838840429</v>
+        <v>2.279397939862545</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.04520432551220211</v>
+        <v>0.04447522348781176</v>
       </c>
       <c r="W63">
-        <v>0.1917229714371498</v>
+        <v>0.1918693751236474</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2054742068736459</v>
+        <v>0.2021601067627807</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6755,22 +6755,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1738682262791597</v>
+        <v>0.1976260853126966</v>
       </c>
       <c r="C64">
-        <v>-6027.049708368225</v>
+        <v>-7147.051936485112</v>
       </c>
       <c r="D64">
-        <v>5862.224291631774</v>
+        <v>4944.899063514886</v>
       </c>
       <c r="E64">
-        <v>12117.374</v>
+        <v>12320.051</v>
       </c>
       <c r="F64">
-        <v>12565.974</v>
+        <v>12768.651</v>
       </c>
       <c r="G64">
         <v>676.7</v>
@@ -6791,45 +6791,45 @@
         <v>510.1</v>
       </c>
       <c r="M64">
-        <v>2523.2475792</v>
+        <v>3010.8479058</v>
       </c>
       <c r="N64">
-        <v>-2013.1475792</v>
+        <v>-2500.7479058</v>
       </c>
       <c r="O64">
-        <v>-442.8924674239999</v>
+        <v>-550.164539276</v>
       </c>
       <c r="P64">
-        <v>-1570.255111776</v>
+        <v>-1950.583366524</v>
       </c>
       <c r="Q64">
-        <v>-1432.055111776</v>
+        <v>-1812.383366524</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1444979307960482</v>
+        <v>0.1475920884757709</v>
       </c>
       <c r="T64">
-        <v>2.279397939862545</v>
+        <v>2.350856546784547</v>
       </c>
       <c r="U64">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04447522348781176</v>
+        <v>0.03727255693780452</v>
       </c>
       <c r="W64">
-        <v>0.1918693751236474</v>
+        <v>0.2270111310740657</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.2021601067627807</v>
+        <v>0.1694207133536569</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6837,22 +6837,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1976260853126966</v>
+        <v>0.1995260853126966</v>
       </c>
       <c r="C65">
-        <v>-7147.051936485112</v>
+        <v>-7410.846138562867</v>
       </c>
       <c r="D65">
-        <v>4944.899063514886</v>
+        <v>4883.781861437131</v>
       </c>
       <c r="E65">
-        <v>12320.051</v>
+        <v>12522.728</v>
       </c>
       <c r="F65">
-        <v>12768.651</v>
+        <v>12971.328</v>
       </c>
       <c r="G65">
         <v>676.7</v>
@@ -6873,37 +6873,37 @@
         <v>510.1</v>
       </c>
       <c r="M65">
-        <v>3010.8479058</v>
+        <v>3058.639142399999</v>
       </c>
       <c r="N65">
-        <v>-2500.7479058</v>
+        <v>-2548.539142399999</v>
       </c>
       <c r="O65">
-        <v>-550.164539276</v>
+        <v>-560.6786113279999</v>
       </c>
       <c r="P65">
-        <v>-1950.583366524</v>
+        <v>-1987.860531072</v>
       </c>
       <c r="Q65">
-        <v>-1812.383366524</v>
+        <v>-1849.660531071999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1475920884757709</v>
+        <v>0.1504196464889867</v>
       </c>
       <c r="T65">
-        <v>2.350856546784547</v>
+        <v>2.416158117528562</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.03727255693780452</v>
+        <v>0.03669017323565133</v>
       </c>
       <c r="W65">
-        <v>0.2270111310740657</v>
+        <v>0.2271484571510334</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1694207133536569</v>
+        <v>0.166773514707506</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6919,22 +6919,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1995260853126966</v>
+        <v>0.2014260853126966</v>
       </c>
       <c r="C66">
-        <v>-7410.846138562867</v>
+        <v>-7673.148011334591</v>
       </c>
       <c r="D66">
-        <v>4883.781861437131</v>
+        <v>4824.156988665409</v>
       </c>
       <c r="E66">
-        <v>12522.728</v>
+        <v>12725.405</v>
       </c>
       <c r="F66">
-        <v>12971.328</v>
+        <v>13174.005</v>
       </c>
       <c r="G66">
         <v>676.7</v>
@@ -6955,37 +6955,37 @@
         <v>510.1</v>
       </c>
       <c r="M66">
-        <v>3058.639142399999</v>
+        <v>3106.430379</v>
       </c>
       <c r="N66">
-        <v>-2548.539142399999</v>
+        <v>-2596.330379</v>
       </c>
       <c r="O66">
-        <v>-560.6786113279999</v>
+        <v>-571.1926833799999</v>
       </c>
       <c r="P66">
-        <v>-1987.860531072</v>
+        <v>-2025.13769562</v>
       </c>
       <c r="Q66">
-        <v>-1849.660531071999</v>
+        <v>-1886.93769562</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1504196464889867</v>
+        <v>0.153408779245815</v>
       </c>
       <c r="T66">
-        <v>2.416158117528562</v>
+        <v>2.485191206600808</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.03669017323565133</v>
+        <v>0.03612570903202592</v>
       </c>
       <c r="W66">
-        <v>0.2271484571510334</v>
+        <v>0.2272815578102483</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.166773514707506</v>
+        <v>0.1642077683273905</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7001,22 +7001,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2014260853126966</v>
+        <v>0.2033260853126966</v>
       </c>
       <c r="C67">
-        <v>-7673.148011334591</v>
+        <v>-7934.011553965097</v>
       </c>
       <c r="D67">
-        <v>4824.156988665409</v>
+        <v>4765.970446034902</v>
       </c>
       <c r="E67">
-        <v>12725.405</v>
+        <v>12928.082</v>
       </c>
       <c r="F67">
-        <v>13174.005</v>
+        <v>13376.682</v>
       </c>
       <c r="G67">
         <v>676.7</v>
@@ -7037,37 +7037,37 @@
         <v>510.1</v>
       </c>
       <c r="M67">
-        <v>3106.430379</v>
+        <v>3154.2216156</v>
       </c>
       <c r="N67">
-        <v>-2596.330379</v>
+        <v>-2644.1216156</v>
       </c>
       <c r="O67">
-        <v>-571.1926833799999</v>
+        <v>-581.706755432</v>
       </c>
       <c r="P67">
-        <v>-2025.13769562</v>
+        <v>-2062.414860168</v>
       </c>
       <c r="Q67">
-        <v>-1886.93769562</v>
+        <v>-1924.214860168</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.153408779245815</v>
+        <v>0.1565737433412801</v>
       </c>
       <c r="T67">
-        <v>2.485191206600808</v>
+        <v>2.558285065618478</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03612570903202592</v>
+        <v>0.03557834980426795</v>
       </c>
       <c r="W67">
-        <v>0.2272815578102483</v>
+        <v>0.2274106251161536</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1642077683273905</v>
+        <v>0.1617197718375816</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7083,22 +7083,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2033260853126966</v>
+        <v>0.2052260853126966</v>
       </c>
       <c r="C68">
-        <v>-7934.011553965097</v>
+        <v>-8193.488191425336</v>
       </c>
       <c r="D68">
-        <v>4765.970446034902</v>
+        <v>4709.170808574662</v>
       </c>
       <c r="E68">
-        <v>12928.082</v>
+        <v>13130.759</v>
       </c>
       <c r="F68">
-        <v>13376.682</v>
+        <v>13579.359</v>
       </c>
       <c r="G68">
         <v>676.7</v>
@@ -7119,37 +7119,37 @@
         <v>510.1</v>
       </c>
       <c r="M68">
-        <v>3154.2216156</v>
+        <v>3202.0128522</v>
       </c>
       <c r="N68">
-        <v>-2644.1216156</v>
+        <v>-2691.9128522</v>
       </c>
       <c r="O68">
-        <v>-581.706755432</v>
+        <v>-592.220827484</v>
       </c>
       <c r="P68">
-        <v>-2062.414860168</v>
+        <v>-2099.692024716</v>
       </c>
       <c r="Q68">
-        <v>-1924.214860168</v>
+        <v>-1961.492024716</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1565737433412801</v>
+        <v>0.159930523442531</v>
       </c>
       <c r="T68">
-        <v>2.558285065618478</v>
+        <v>2.635808855485705</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03557834980426795</v>
+        <v>0.03504732965793559</v>
       </c>
       <c r="W68">
-        <v>0.2274106251161536</v>
+        <v>0.2275358396666588</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1617197718375816</v>
+        <v>0.1593060438997073</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7165,22 +7165,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2052260853126966</v>
+        <v>0.2071260853126966</v>
       </c>
       <c r="C69">
-        <v>-8193.488191425336</v>
+        <v>-8451.626926078783</v>
       </c>
       <c r="D69">
-        <v>4709.170808574662</v>
+        <v>4653.709073921215</v>
       </c>
       <c r="E69">
-        <v>13130.759</v>
+        <v>13333.436</v>
       </c>
       <c r="F69">
-        <v>13579.359</v>
+        <v>13782.036</v>
       </c>
       <c r="G69">
         <v>676.7</v>
@@ -7201,37 +7201,37 @@
         <v>510.1</v>
       </c>
       <c r="M69">
-        <v>3202.0128522</v>
+        <v>3249.8040888</v>
       </c>
       <c r="N69">
-        <v>-2691.9128522</v>
+        <v>-2739.7040888</v>
       </c>
       <c r="O69">
-        <v>-592.220827484</v>
+        <v>-602.7348995359999</v>
       </c>
       <c r="P69">
-        <v>-2099.692024716</v>
+        <v>-2136.969189264</v>
       </c>
       <c r="Q69">
-        <v>-1961.492024716</v>
+        <v>-1998.769189264</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.159930523442531</v>
+        <v>0.1634971023001101</v>
       </c>
       <c r="T69">
-        <v>2.635808855485705</v>
+        <v>2.718177882219633</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.03504732965793559</v>
+        <v>0.03453192775120125</v>
       </c>
       <c r="W69">
-        <v>0.2275358396666588</v>
+        <v>0.2276573714362667</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7239,7 +7239,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1593060438997073</v>
+        <v>0.1569633079600057</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7247,22 +7247,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2071260853126966</v>
+        <v>0.2090260853126966</v>
       </c>
       <c r="C70">
-        <v>-8451.626926078783</v>
+        <v>-8708.474478680786</v>
       </c>
       <c r="D70">
-        <v>4653.709073921215</v>
+        <v>4599.538521319213</v>
       </c>
       <c r="E70">
-        <v>13333.436</v>
+        <v>13536.113</v>
       </c>
       <c r="F70">
-        <v>13782.036</v>
+        <v>13984.713</v>
       </c>
       <c r="G70">
         <v>676.7</v>
@@ -7283,37 +7283,37 @@
         <v>510.1</v>
       </c>
       <c r="M70">
-        <v>3249.8040888</v>
+        <v>3297.5953254</v>
       </c>
       <c r="N70">
-        <v>-2739.7040888</v>
+        <v>-2787.4953254</v>
       </c>
       <c r="O70">
-        <v>-602.7348995359999</v>
+        <v>-613.248971588</v>
       </c>
       <c r="P70">
-        <v>-2136.969189264</v>
+        <v>-2174.246353812</v>
       </c>
       <c r="Q70">
-        <v>-1998.769189264</v>
+        <v>-2036.046353812</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1634971023001101</v>
+        <v>0.1672937830194685</v>
       </c>
       <c r="T70">
-        <v>2.718177882219633</v>
+        <v>2.80586103971059</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.03453192775120125</v>
+        <v>0.03403146503016934</v>
       </c>
       <c r="W70">
-        <v>0.2276573714362667</v>
+        <v>0.2277753805458861</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1569633079600057</v>
+        <v>0.1546884774098606</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7329,22 +7329,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2090260853126966</v>
+        <v>0.2109260853126966</v>
       </c>
       <c r="C71">
-        <v>-8708.474478680786</v>
+        <v>-8964.075419643581</v>
       </c>
       <c r="D71">
-        <v>4599.538521319213</v>
+        <v>4546.61458035642</v>
       </c>
       <c r="E71">
-        <v>13536.113</v>
+        <v>13738.79</v>
       </c>
       <c r="F71">
-        <v>13984.713</v>
+        <v>14187.39</v>
       </c>
       <c r="G71">
         <v>676.7</v>
@@ -7365,37 +7365,37 @@
         <v>510.1</v>
       </c>
       <c r="M71">
-        <v>3297.5953254</v>
+        <v>3345.386562</v>
       </c>
       <c r="N71">
-        <v>-2787.4953254</v>
+        <v>-2835.286562</v>
       </c>
       <c r="O71">
-        <v>-613.248971588</v>
+        <v>-623.7630436400001</v>
       </c>
       <c r="P71">
-        <v>-2174.246353812</v>
+        <v>-2211.52351836</v>
       </c>
       <c r="Q71">
-        <v>-2036.046353812</v>
+        <v>-2073.32351836</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1672937830194685</v>
+        <v>0.1713435757867841</v>
       </c>
       <c r="T71">
-        <v>2.80586103971059</v>
+        <v>2.899389741034275</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03403146503016934</v>
+        <v>0.03354530124402406</v>
       </c>
       <c r="W71">
-        <v>0.2277753805458861</v>
+        <v>0.2278900179666591</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1546884774098606</v>
+        <v>0.1524786420182912</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7411,22 +7411,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2109260853126966</v>
+        <v>0.2128260853126966</v>
       </c>
       <c r="C72">
-        <v>-8964.075419643581</v>
+        <v>-9218.472291342092</v>
       </c>
       <c r="D72">
-        <v>4546.61458035642</v>
+        <v>4494.894708657906</v>
       </c>
       <c r="E72">
-        <v>13738.79</v>
+        <v>13941.467</v>
       </c>
       <c r="F72">
-        <v>14187.39</v>
+        <v>14390.067</v>
       </c>
       <c r="G72">
         <v>676.7</v>
@@ -7447,37 +7447,37 @@
         <v>510.1</v>
       </c>
       <c r="M72">
-        <v>3345.386562</v>
+        <v>3393.1777986</v>
       </c>
       <c r="N72">
-        <v>-2835.286562</v>
+        <v>-2883.0777986</v>
       </c>
       <c r="O72">
-        <v>-623.7630436400001</v>
+        <v>-634.2771156919999</v>
       </c>
       <c r="P72">
-        <v>-2211.52351836</v>
+        <v>-2248.800682908</v>
       </c>
       <c r="Q72">
-        <v>-2073.32351836</v>
+        <v>-2110.600682908</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1713435757867841</v>
+        <v>0.1756726646070181</v>
       </c>
       <c r="T72">
-        <v>2.899389741034275</v>
+        <v>2.999368697621664</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03354530124402406</v>
+        <v>0.0330728322124181</v>
       </c>
       <c r="W72">
-        <v>0.2278900179666591</v>
+        <v>0.2280014261643118</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1524786420182912</v>
+        <v>0.1503310555109914</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7493,22 +7493,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2128260853126966</v>
+        <v>0.2147260853126966</v>
       </c>
       <c r="C73">
-        <v>-9218.472291342086</v>
+        <v>-9471.705722165909</v>
       </c>
       <c r="D73">
-        <v>4494.894708657911</v>
+        <v>4444.338277834089</v>
       </c>
       <c r="E73">
-        <v>13941.467</v>
+        <v>14144.144</v>
       </c>
       <c r="F73">
-        <v>14390.067</v>
+        <v>14592.744</v>
       </c>
       <c r="G73">
         <v>676.7</v>
@@ -7529,37 +7529,37 @@
         <v>510.1</v>
       </c>
       <c r="M73">
-        <v>3393.177798599999</v>
+        <v>3440.969035199999</v>
       </c>
       <c r="N73">
-        <v>-2883.077798599999</v>
+        <v>-2930.869035199999</v>
       </c>
       <c r="O73">
-        <v>-634.2771156919998</v>
+        <v>-644.7911877439999</v>
       </c>
       <c r="P73">
-        <v>-2248.800682908</v>
+        <v>-2286.077847455999</v>
       </c>
       <c r="Q73">
-        <v>-2110.600682908</v>
+        <v>-2147.877847455999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.175672664607018</v>
+        <v>0.1803109740572686</v>
       </c>
       <c r="T73">
-        <v>2.999368697621664</v>
+        <v>3.106489008251008</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.0330728322124181</v>
+        <v>0.03261348732057896</v>
       </c>
       <c r="W73">
-        <v>0.2280014261643118</v>
+        <v>0.2281097396898075</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1503310555109914</v>
+        <v>0.1482431241844498</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7575,22 +7575,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2147260853126966</v>
+        <v>0.2166260853126966</v>
       </c>
       <c r="C74">
-        <v>-9471.705722165909</v>
+        <v>-9723.814532960072</v>
       </c>
       <c r="D74">
-        <v>4444.338277834089</v>
+        <v>4394.906467039925</v>
       </c>
       <c r="E74">
-        <v>14144.144</v>
+        <v>14346.821</v>
       </c>
       <c r="F74">
-        <v>14592.744</v>
+        <v>14795.421</v>
       </c>
       <c r="G74">
         <v>676.7</v>
@@ -7611,37 +7611,37 @@
         <v>510.1</v>
       </c>
       <c r="M74">
-        <v>3440.969035199999</v>
+        <v>3488.760271799999</v>
       </c>
       <c r="N74">
-        <v>-2930.869035199999</v>
+        <v>-2978.660271799999</v>
       </c>
       <c r="O74">
-        <v>-644.7911877439999</v>
+        <v>-655.3052597959999</v>
       </c>
       <c r="P74">
-        <v>-2286.077847455999</v>
+        <v>-2323.355012003999</v>
       </c>
       <c r="Q74">
-        <v>-2147.877847455999</v>
+        <v>-2185.155012004</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1803109740572686</v>
+        <v>0.1852928619853156</v>
       </c>
       <c r="T74">
-        <v>3.106489008251008</v>
+        <v>3.221544156704749</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03261348732057896</v>
+        <v>0.03216672722029706</v>
       </c>
       <c r="W74">
-        <v>0.2281097396898075</v>
+        <v>0.228215085721454</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1482431241844498</v>
+        <v>0.1462123964558957</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7657,22 +7657,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2166260853126966</v>
+        <v>0.2185260853126966</v>
       </c>
       <c r="C75">
-        <v>-9723.814532960072</v>
+        <v>-9974.835836440692</v>
       </c>
       <c r="D75">
-        <v>4394.906467039925</v>
+        <v>4346.562163559307</v>
       </c>
       <c r="E75">
-        <v>14346.821</v>
+        <v>14549.498</v>
       </c>
       <c r="F75">
-        <v>14795.421</v>
+        <v>14998.098</v>
       </c>
       <c r="G75">
         <v>676.7</v>
@@ -7693,37 +7693,37 @@
         <v>510.1</v>
       </c>
       <c r="M75">
-        <v>3488.760271799999</v>
+        <v>3536.5515084</v>
       </c>
       <c r="N75">
-        <v>-2978.660271799999</v>
+        <v>-3026.4515084</v>
       </c>
       <c r="O75">
-        <v>-655.3052597959999</v>
+        <v>-665.819331848</v>
       </c>
       <c r="P75">
-        <v>-2323.355012003999</v>
+        <v>-2360.632176552</v>
       </c>
       <c r="Q75">
-        <v>-2185.155012004</v>
+        <v>-2222.432176552</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1852928619853156</v>
+        <v>0.190657972061674</v>
       </c>
       <c r="T75">
-        <v>3.221544156704749</v>
+        <v>3.345449701193394</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03216672722029706</v>
+        <v>0.03173204171732006</v>
       </c>
       <c r="W75">
-        <v>0.228215085721454</v>
+        <v>0.228317584563056</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1462123964558957</v>
+        <v>0.1442365532605457</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7739,22 +7739,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2185260853126966</v>
+        <v>0.2204260853126966</v>
       </c>
       <c r="C76">
-        <v>-9974.835836440692</v>
+        <v>-10224.80513012049</v>
       </c>
       <c r="D76">
-        <v>4346.562163559307</v>
+        <v>4299.269869879507</v>
       </c>
       <c r="E76">
-        <v>14549.498</v>
+        <v>14752.175</v>
       </c>
       <c r="F76">
-        <v>14998.098</v>
+        <v>15200.775</v>
       </c>
       <c r="G76">
         <v>676.7</v>
@@ -7775,37 +7775,37 @@
         <v>510.1</v>
       </c>
       <c r="M76">
-        <v>3536.5515084</v>
+        <v>3584.342744999999</v>
       </c>
       <c r="N76">
-        <v>-3026.4515084</v>
+        <v>-3074.242745</v>
       </c>
       <c r="O76">
-        <v>-665.819331848</v>
+        <v>-676.3334038999999</v>
       </c>
       <c r="P76">
-        <v>-2360.632176552</v>
+        <v>-2397.909341099999</v>
       </c>
       <c r="Q76">
-        <v>-2222.432176552</v>
+        <v>-2259.7093411</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.190657972061674</v>
+        <v>0.1964522909441409</v>
       </c>
       <c r="T76">
-        <v>3.345449701193394</v>
+        <v>3.47926768924113</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03173204171732006</v>
+        <v>0.0313089478277558</v>
       </c>
       <c r="W76">
-        <v>0.228317584563056</v>
+        <v>0.2284173501022152</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1442365532605457</v>
+        <v>0.1423133992170718</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7821,22 +7821,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2204260853126966</v>
+        <v>0.2223260853126966</v>
       </c>
       <c r="C77">
-        <v>-10224.80513012049</v>
+        <v>-10473.75638323329</v>
       </c>
       <c r="D77">
-        <v>4299.269869879507</v>
+        <v>4252.995616766707</v>
       </c>
       <c r="E77">
-        <v>14752.175</v>
+        <v>14954.852</v>
       </c>
       <c r="F77">
-        <v>15200.775</v>
+        <v>15403.452</v>
       </c>
       <c r="G77">
         <v>676.7</v>
@@ -7857,37 +7857,37 @@
         <v>510.1</v>
       </c>
       <c r="M77">
-        <v>3584.342744999999</v>
+        <v>3632.1339816</v>
       </c>
       <c r="N77">
-        <v>-3074.242745</v>
+        <v>-3122.0339816</v>
       </c>
       <c r="O77">
-        <v>-676.3334038999999</v>
+        <v>-686.847475952</v>
       </c>
       <c r="P77">
-        <v>-2397.909341099999</v>
+        <v>-2435.186505648</v>
       </c>
       <c r="Q77">
-        <v>-2259.7093411</v>
+        <v>-2296.986505648</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1964522909441409</v>
+        <v>0.2027294697334801</v>
       </c>
       <c r="T77">
-        <v>3.47926768924113</v>
+        <v>3.624237176292844</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.0313089478277558</v>
+        <v>0.03089698798791691</v>
       </c>
       <c r="W77">
-        <v>0.2284173501022152</v>
+        <v>0.2285144902324492</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7895,7 +7895,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1423133992170718</v>
+        <v>0.1404408544905313</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7903,22 +7903,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2223260853126966</v>
+        <v>0.2242260853126966</v>
       </c>
       <c r="C78">
-        <v>-10473.75638323329</v>
+        <v>-10721.72211810462</v>
       </c>
       <c r="D78">
-        <v>4252.995616766707</v>
+        <v>4207.706881895375</v>
       </c>
       <c r="E78">
-        <v>14954.852</v>
+        <v>15157.529</v>
       </c>
       <c r="F78">
-        <v>15403.452</v>
+        <v>15606.129</v>
       </c>
       <c r="G78">
         <v>676.7</v>
@@ -7939,37 +7939,37 @@
         <v>510.1</v>
       </c>
       <c r="M78">
-        <v>3632.1339816</v>
+        <v>3679.9252182</v>
       </c>
       <c r="N78">
-        <v>-3122.0339816</v>
+        <v>-3169.8252182</v>
       </c>
       <c r="O78">
-        <v>-686.847475952</v>
+        <v>-697.361548004</v>
       </c>
       <c r="P78">
-        <v>-2435.186505648</v>
+        <v>-2472.463670196</v>
       </c>
       <c r="Q78">
-        <v>-2296.986505648</v>
+        <v>-2334.263670196</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2027294697334801</v>
+        <v>0.2095524901566749</v>
       </c>
       <c r="T78">
-        <v>3.624237176292844</v>
+        <v>3.781812705696881</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03089698798791691</v>
+        <v>0.03049572840365824</v>
       </c>
       <c r="W78">
-        <v>0.2285144902324492</v>
+        <v>0.2286091072424174</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1404408544905313</v>
+        <v>0.1386169472893556</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7985,22 +7985,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2242260853126966</v>
+        <v>0.2261260853126966</v>
       </c>
       <c r="C79">
-        <v>-10721.72211810462</v>
+        <v>-10968.73348637829</v>
       </c>
       <c r="D79">
-        <v>4207.706881895375</v>
+        <v>4163.372513621708</v>
       </c>
       <c r="E79">
-        <v>15157.529</v>
+        <v>15360.206</v>
       </c>
       <c r="F79">
-        <v>15606.129</v>
+        <v>15808.806</v>
       </c>
       <c r="G79">
         <v>676.7</v>
@@ -8021,37 +8021,37 @@
         <v>510.1</v>
       </c>
       <c r="M79">
-        <v>3679.9252182</v>
+        <v>3727.7164548</v>
       </c>
       <c r="N79">
-        <v>-3169.8252182</v>
+        <v>-3217.6164548</v>
       </c>
       <c r="O79">
-        <v>-697.361548004</v>
+        <v>-707.875620056</v>
       </c>
       <c r="P79">
-        <v>-2472.463670196</v>
+        <v>-2509.740834744</v>
       </c>
       <c r="Q79">
-        <v>-2334.263670196</v>
+        <v>-2371.540834744</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2095524901566749</v>
+        <v>0.2169957851637965</v>
       </c>
       <c r="T79">
-        <v>3.781812705696881</v>
+        <v>3.953713283228557</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03049572840365824</v>
+        <v>0.03010475752668826</v>
       </c>
       <c r="W79">
-        <v>0.2286091072424174</v>
+        <v>0.2287012981752069</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1386169472893556</v>
+        <v>0.136839806939492</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8067,22 +8067,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2261260853126966</v>
+        <v>0.2280260853126966</v>
       </c>
       <c r="C80">
-        <v>-10968.73348637829</v>
+        <v>-11214.82034047414</v>
       </c>
       <c r="D80">
-        <v>4163.372513621708</v>
+        <v>4119.962659525863</v>
       </c>
       <c r="E80">
-        <v>15360.206</v>
+        <v>15562.883</v>
       </c>
       <c r="F80">
-        <v>15808.806</v>
+        <v>16011.483</v>
       </c>
       <c r="G80">
         <v>676.7</v>
@@ -8103,37 +8103,37 @@
         <v>510.1</v>
       </c>
       <c r="M80">
-        <v>3727.7164548</v>
+        <v>3775.5076914</v>
       </c>
       <c r="N80">
-        <v>-3217.6164548</v>
+        <v>-3265.4076914</v>
       </c>
       <c r="O80">
-        <v>-707.875620056</v>
+        <v>-718.389692108</v>
       </c>
       <c r="P80">
-        <v>-2509.740834744</v>
+        <v>-2547.017999292</v>
       </c>
       <c r="Q80">
-        <v>-2371.540834744</v>
+        <v>-2408.817999292</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2169957851637965</v>
+        <v>0.2251479654096916</v>
       </c>
       <c r="T80">
-        <v>3.953713283228557</v>
+        <v>4.141985344334679</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03010475752668826</v>
+        <v>0.02972368464660361</v>
       </c>
       <c r="W80">
-        <v>0.2287012981752069</v>
+        <v>0.2287911551603309</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.136839806939492</v>
+        <v>0.1351076574845618</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8149,22 +8149,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2280260853126966</v>
+        <v>0.2299260853126966</v>
       </c>
       <c r="C81">
-        <v>-11214.82034047414</v>
+        <v>-11460.01130062163</v>
       </c>
       <c r="D81">
-        <v>4119.962659525863</v>
+        <v>4077.448699378366</v>
       </c>
       <c r="E81">
-        <v>15562.883</v>
+        <v>15765.56</v>
       </c>
       <c r="F81">
-        <v>16011.483</v>
+        <v>16214.16</v>
       </c>
       <c r="G81">
         <v>676.7</v>
@@ -8185,37 +8185,37 @@
         <v>510.1</v>
       </c>
       <c r="M81">
-        <v>3775.5076914</v>
+        <v>3823.298928</v>
       </c>
       <c r="N81">
-        <v>-3265.4076914</v>
+        <v>-3313.198928</v>
       </c>
       <c r="O81">
-        <v>-718.389692108</v>
+        <v>-728.9037641599999</v>
       </c>
       <c r="P81">
-        <v>-2547.017999292</v>
+        <v>-2584.29516384</v>
       </c>
       <c r="Q81">
-        <v>-2408.817999292</v>
+        <v>-2446.09516384</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2251479654096916</v>
+        <v>0.2341153636801762</v>
       </c>
       <c r="T81">
-        <v>4.141985344334679</v>
+        <v>4.349084611551413</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02972368464660361</v>
+        <v>0.02935213858852106</v>
       </c>
       <c r="W81">
-        <v>0.2287911551603309</v>
+        <v>0.2288787657208267</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1351076574845618</v>
+        <v>0.1334188117660048</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8231,22 +8231,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2299260853126966</v>
+        <v>0.2318260853126966</v>
       </c>
       <c r="C82">
-        <v>-11460.01130062163</v>
+        <v>-11704.33381778551</v>
       </c>
       <c r="D82">
-        <v>4077.448699378366</v>
+        <v>4035.803182214486</v>
       </c>
       <c r="E82">
-        <v>15765.56</v>
+        <v>15968.237</v>
       </c>
       <c r="F82">
-        <v>16214.16</v>
+        <v>16416.837</v>
       </c>
       <c r="G82">
         <v>676.7</v>
@@ -8267,37 +8267,37 @@
         <v>510.1</v>
       </c>
       <c r="M82">
-        <v>3823.298928</v>
+        <v>3871.0901646</v>
       </c>
       <c r="N82">
-        <v>-3313.198928</v>
+        <v>-3360.9901646</v>
       </c>
       <c r="O82">
-        <v>-728.9037641599999</v>
+        <v>-739.4178362120001</v>
       </c>
       <c r="P82">
-        <v>-2584.29516384</v>
+        <v>-2621.572328388</v>
       </c>
       <c r="Q82">
-        <v>-2446.09516384</v>
+        <v>-2483.372328388</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2341153636801762</v>
+        <v>0.2440266986107118</v>
       </c>
       <c r="T82">
-        <v>4.349084611551413</v>
+        <v>4.577983801633067</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02935213858852106</v>
+        <v>0.02898976650718129</v>
       </c>
       <c r="W82">
-        <v>0.2288787657208267</v>
+        <v>0.2289642130576066</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1334188117660048</v>
+        <v>0.1317716659417332</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8313,22 +8313,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2318260853126966</v>
+        <v>0.2337260853126966</v>
       </c>
       <c r="C83">
-        <v>-11704.33381778551</v>
+        <v>-11947.81423277417</v>
       </c>
       <c r="D83">
-        <v>4035.803182214486</v>
+        <v>3994.999767225832</v>
       </c>
       <c r="E83">
-        <v>15968.237</v>
+        <v>16170.914</v>
       </c>
       <c r="F83">
-        <v>16416.837</v>
+        <v>16619.514</v>
       </c>
       <c r="G83">
         <v>676.7</v>
@@ -8349,37 +8349,37 @@
         <v>510.1</v>
       </c>
       <c r="M83">
-        <v>3871.0901646</v>
+        <v>3918.8814012</v>
       </c>
       <c r="N83">
-        <v>-3360.9901646</v>
+        <v>-3408.7814012</v>
       </c>
       <c r="O83">
-        <v>-739.4178362120001</v>
+        <v>-749.931908264</v>
       </c>
       <c r="P83">
-        <v>-2621.572328388</v>
+        <v>-2658.849492936</v>
       </c>
       <c r="Q83">
-        <v>-2483.372328388</v>
+        <v>-2520.649492936</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2440266986107118</v>
+        <v>0.2550392929779736</v>
       </c>
       <c r="T83">
-        <v>4.577983801633067</v>
+        <v>4.832316235057126</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02898976650718129</v>
+        <v>0.02863623276928884</v>
       </c>
       <c r="W83">
-        <v>0.2289642130576066</v>
+        <v>0.2290475763130017</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1317716659417332</v>
+        <v>0.1301646944058583</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8395,22 +8395,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2337260853126966</v>
+        <v>0.2356260853126966</v>
       </c>
       <c r="C84">
-        <v>-11947.81423277417</v>
+        <v>-12190.47783179835</v>
       </c>
       <c r="D84">
-        <v>3994.999767225832</v>
+        <v>3955.013168201646</v>
       </c>
       <c r="E84">
-        <v>16170.914</v>
+        <v>16373.591</v>
       </c>
       <c r="F84">
-        <v>16619.514</v>
+        <v>16822.191</v>
       </c>
       <c r="G84">
         <v>676.7</v>
@@ -8431,37 +8431,37 @@
         <v>510.1</v>
       </c>
       <c r="M84">
-        <v>3918.8814012</v>
+        <v>3966.6726378</v>
       </c>
       <c r="N84">
-        <v>-3408.7814012</v>
+        <v>-3456.5726378</v>
       </c>
       <c r="O84">
-        <v>-749.931908264</v>
+        <v>-760.445980316</v>
       </c>
       <c r="P84">
-        <v>-2658.849492936</v>
+        <v>-2696.126657484</v>
       </c>
       <c r="Q84">
-        <v>-2520.649492936</v>
+        <v>-2557.926657484</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2550392929779736</v>
+        <v>0.2673474866825603</v>
       </c>
       <c r="T84">
-        <v>4.832316235057126</v>
+        <v>5.116570131236958</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02863623276928884</v>
+        <v>0.0282912179166468</v>
       </c>
       <c r="W84">
-        <v>0.2290475763130017</v>
+        <v>0.2291289308152547</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1301646944058583</v>
+        <v>0.1285964450756673</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8477,22 +8477,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2356260853126966</v>
+        <v>0.2375260853126966</v>
       </c>
       <c r="C85">
-        <v>-12190.47783179835</v>
+        <v>-12432.34889872632</v>
       </c>
       <c r="D85">
-        <v>3955.013168201646</v>
+        <v>3915.819101273679</v>
       </c>
       <c r="E85">
-        <v>16373.591</v>
+        <v>16576.268</v>
       </c>
       <c r="F85">
-        <v>16822.191</v>
+        <v>17024.868</v>
       </c>
       <c r="G85">
         <v>676.7</v>
@@ -8513,37 +8513,37 @@
         <v>510.1</v>
       </c>
       <c r="M85">
-        <v>3966.6726378</v>
+        <v>4014.4638744</v>
       </c>
       <c r="N85">
-        <v>-3456.5726378</v>
+        <v>-3504.3638744</v>
       </c>
       <c r="O85">
-        <v>-760.445980316</v>
+        <v>-770.960052368</v>
       </c>
       <c r="P85">
-        <v>-2696.126657484</v>
+        <v>-2733.403822032</v>
       </c>
       <c r="Q85">
-        <v>-2557.926657484</v>
+        <v>-2595.203822032</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2673474866825603</v>
+        <v>0.2811942046002203</v>
       </c>
       <c r="T85">
-        <v>5.116570131236958</v>
+        <v>5.436355764439269</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0282912179166468</v>
+        <v>0.02795441770335339</v>
       </c>
       <c r="W85">
-        <v>0.2291289308152547</v>
+        <v>0.2292083483055493</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1285964450756673</v>
+        <v>0.1270655350152426</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8559,22 +8559,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2375260853126966</v>
+        <v>0.2394260853126966</v>
       </c>
       <c r="C86">
-        <v>-12432.34889872632</v>
+        <v>-12673.45076426241</v>
       </c>
       <c r="D86">
-        <v>3915.819101273681</v>
+        <v>3877.394235737591</v>
       </c>
       <c r="E86">
-        <v>16576.268</v>
+        <v>16778.945</v>
       </c>
       <c r="F86">
-        <v>17024.868</v>
+        <v>17227.545</v>
       </c>
       <c r="G86">
         <v>676.7</v>
@@ -8595,37 +8595,37 @@
         <v>510.1</v>
       </c>
       <c r="M86">
-        <v>4014.4638744</v>
+        <v>4062.255111</v>
       </c>
       <c r="N86">
-        <v>-3504.3638744</v>
+        <v>-3552.155111</v>
       </c>
       <c r="O86">
-        <v>-770.960052368</v>
+        <v>-781.4741244200001</v>
       </c>
       <c r="P86">
-        <v>-2733.403822032</v>
+        <v>-2770.68098658</v>
       </c>
       <c r="Q86">
-        <v>-2595.203822032</v>
+        <v>-2632.48098658</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2811942046002202</v>
+        <v>0.2968871515735682</v>
       </c>
       <c r="T86">
-        <v>5.436355764439265</v>
+        <v>5.798779482068549</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02795441770335339</v>
+        <v>0.02762554220096099</v>
       </c>
       <c r="W86">
-        <v>0.2292083483055493</v>
+        <v>0.2292858971490134</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1270655350152426</v>
+        <v>0.1255706463680045</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8641,22 +8641,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2394260853126966</v>
+        <v>0.2413260853126966</v>
       </c>
       <c r="C87">
-        <v>-12673.45076426241</v>
+        <v>-12913.80585225829</v>
       </c>
       <c r="D87">
-        <v>3877.394235737591</v>
+        <v>3839.716147741709</v>
       </c>
       <c r="E87">
-        <v>16778.945</v>
+        <v>16981.622</v>
       </c>
       <c r="F87">
-        <v>17227.545</v>
+        <v>17430.222</v>
       </c>
       <c r="G87">
         <v>676.7</v>
@@ -8677,37 +8677,37 @@
         <v>510.1</v>
       </c>
       <c r="M87">
-        <v>4062.255111</v>
+        <v>4110.0463476</v>
       </c>
       <c r="N87">
-        <v>-3552.155111</v>
+        <v>-3599.9463476</v>
       </c>
       <c r="O87">
-        <v>-781.4741244200001</v>
+        <v>-791.9881964719999</v>
       </c>
       <c r="P87">
-        <v>-2770.68098658</v>
+        <v>-2807.958151128</v>
       </c>
       <c r="Q87">
-        <v>-2632.48098658</v>
+        <v>-2669.758151128</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2968871515735682</v>
+        <v>0.3148219481145373</v>
       </c>
       <c r="T87">
-        <v>5.798779482068549</v>
+        <v>6.212978016502017</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02762554220096099</v>
+        <v>0.0273043149660661</v>
       </c>
       <c r="W87">
-        <v>0.2292858971490134</v>
+        <v>0.2293616425310016</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1255706463680045</v>
+        <v>0.1241105225730277</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8723,22 +8723,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2413260853126966</v>
+        <v>0.2432260853126966</v>
       </c>
       <c r="C88">
-        <v>-12913.80585225829</v>
+        <v>-13153.43572335004</v>
       </c>
       <c r="D88">
-        <v>3839.716147741709</v>
+        <v>3802.763276649958</v>
       </c>
       <c r="E88">
-        <v>16981.622</v>
+        <v>17184.299</v>
       </c>
       <c r="F88">
-        <v>17430.222</v>
+        <v>17632.899</v>
       </c>
       <c r="G88">
         <v>676.7</v>
@@ -8759,37 +8759,37 @@
         <v>510.1</v>
       </c>
       <c r="M88">
-        <v>4110.0463476</v>
+        <v>4157.8375842</v>
       </c>
       <c r="N88">
-        <v>-3599.9463476</v>
+        <v>-3647.7375842</v>
       </c>
       <c r="O88">
-        <v>-791.9881964719999</v>
+        <v>-802.502268524</v>
       </c>
       <c r="P88">
-        <v>-2807.958151128</v>
+        <v>-2845.235315676</v>
       </c>
       <c r="Q88">
-        <v>-2669.758151128</v>
+        <v>-2707.035315676</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3148219481145373</v>
+        <v>0.3355159441233479</v>
       </c>
       <c r="T88">
-        <v>6.212978016502017</v>
+        <v>6.690899402386788</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0273043149660661</v>
+        <v>0.02699047226530672</v>
       </c>
       <c r="W88">
-        <v>0.2293616425310016</v>
+        <v>0.2294356466398407</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1241105225730277</v>
+        <v>0.1226839648423033</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8805,22 +8805,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2432260853126966</v>
+        <v>0.2451260853126966</v>
       </c>
       <c r="C89">
-        <v>-13153.43572335004</v>
+        <v>-13392.36111609954</v>
       </c>
       <c r="D89">
-        <v>3802.763276649958</v>
+        <v>3766.514883900457</v>
       </c>
       <c r="E89">
-        <v>17184.299</v>
+        <v>17386.976</v>
       </c>
       <c r="F89">
-        <v>17632.899</v>
+        <v>17835.576</v>
       </c>
       <c r="G89">
         <v>676.7</v>
@@ -8841,37 +8841,37 @@
         <v>510.1</v>
       </c>
       <c r="M89">
-        <v>4157.8375842</v>
+        <v>4205.6288208</v>
       </c>
       <c r="N89">
-        <v>-3647.7375842</v>
+        <v>-3695.5288208</v>
       </c>
       <c r="O89">
-        <v>-802.502268524</v>
+        <v>-813.0163405759999</v>
       </c>
       <c r="P89">
-        <v>-2845.235315676</v>
+        <v>-2882.512480224</v>
       </c>
       <c r="Q89">
-        <v>-2707.035315676</v>
+        <v>-2744.312480224</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3355159441233479</v>
+        <v>0.3596589394669603</v>
       </c>
       <c r="T89">
-        <v>6.690899402386788</v>
+        <v>7.248474352585688</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02699047226530672</v>
+        <v>0.02668376235320096</v>
       </c>
       <c r="W89">
-        <v>0.2294356466398407</v>
+        <v>0.2295079688371152</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8879,7 +8879,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1226839648423033</v>
+        <v>0.1212898288781862</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8887,22 +8887,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2451260853126966</v>
+        <v>0.2470260853126967</v>
       </c>
       <c r="C90">
-        <v>-13392.36111609954</v>
+        <v>-13630.60198580505</v>
       </c>
       <c r="D90">
-        <v>3766.514883900457</v>
+        <v>3730.951014194946</v>
       </c>
       <c r="E90">
-        <v>17386.976</v>
+        <v>17589.653</v>
       </c>
       <c r="F90">
-        <v>17835.576</v>
+        <v>18038.253</v>
       </c>
       <c r="G90">
         <v>676.7</v>
@@ -8923,37 +8923,37 @@
         <v>510.1</v>
       </c>
       <c r="M90">
-        <v>4205.6288208</v>
+        <v>4253.4200574</v>
       </c>
       <c r="N90">
-        <v>-3695.5288208</v>
+        <v>-3743.3200574</v>
       </c>
       <c r="O90">
-        <v>-813.0163405759999</v>
+        <v>-823.5304126279999</v>
       </c>
       <c r="P90">
-        <v>-2882.512480224</v>
+        <v>-2919.789644772</v>
       </c>
       <c r="Q90">
-        <v>-2744.312480224</v>
+        <v>-2781.589644772</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3596589394669603</v>
+        <v>0.388191570327593</v>
       </c>
       <c r="T90">
-        <v>7.248474352585688</v>
+        <v>7.907426566457114</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02668376235320096</v>
+        <v>0.02638394479867062</v>
       </c>
       <c r="W90">
-        <v>0.2295079688371152</v>
+        <v>0.2295786658164735</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1212898288781862</v>
+        <v>0.1199270218121391</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8969,22 +8969,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2470260853126967</v>
+        <v>0.2489260853126966</v>
       </c>
       <c r="C91">
-        <v>-13630.60198580505</v>
+        <v>-13868.17754113366</v>
       </c>
       <c r="D91">
-        <v>3730.951014194946</v>
+        <v>3696.052458866332</v>
       </c>
       <c r="E91">
-        <v>17589.653</v>
+        <v>17792.33</v>
       </c>
       <c r="F91">
-        <v>18038.253</v>
+        <v>18240.93</v>
       </c>
       <c r="G91">
         <v>676.7</v>
@@ -9005,37 +9005,37 @@
         <v>510.1</v>
       </c>
       <c r="M91">
-        <v>4253.4200574</v>
+        <v>4301.211294</v>
       </c>
       <c r="N91">
-        <v>-3743.3200574</v>
+        <v>-3791.111294</v>
       </c>
       <c r="O91">
-        <v>-823.5304126279999</v>
+        <v>-834.04448468</v>
       </c>
       <c r="P91">
-        <v>-2919.789644772</v>
+        <v>-2957.06680932</v>
       </c>
       <c r="Q91">
-        <v>-2781.589644772</v>
+        <v>-2818.86680932</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.388191570327593</v>
+        <v>0.4224307273603523</v>
       </c>
       <c r="T91">
-        <v>7.907426566457114</v>
+        <v>8.698169223102825</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02638394479867062</v>
+        <v>0.02609078985646316</v>
       </c>
       <c r="W91">
-        <v>0.2295786658164735</v>
+        <v>0.229647791751846</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1199270218121391</v>
+        <v>0.1185944993475598</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9051,22 +9051,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2489260853126966</v>
+        <v>0.2508260853126966</v>
       </c>
       <c r="C92">
-        <v>-13868.17754113366</v>
+        <v>-14105.10627871689</v>
       </c>
       <c r="D92">
-        <v>3696.052458866332</v>
+        <v>3661.800721283107</v>
       </c>
       <c r="E92">
-        <v>17792.33</v>
+        <v>17995.007</v>
       </c>
       <c r="F92">
-        <v>18240.93</v>
+        <v>18443.607</v>
       </c>
       <c r="G92">
         <v>676.7</v>
@@ -9087,37 +9087,37 @@
         <v>510.1</v>
       </c>
       <c r="M92">
-        <v>4301.211294</v>
+        <v>4349.002530599999</v>
       </c>
       <c r="N92">
-        <v>-3791.111294</v>
+        <v>-3838.902530599999</v>
       </c>
       <c r="O92">
-        <v>-834.04448468</v>
+        <v>-844.5585567319998</v>
       </c>
       <c r="P92">
-        <v>-2957.06680932</v>
+        <v>-2994.343973867999</v>
       </c>
       <c r="Q92">
-        <v>-2818.86680932</v>
+        <v>-2856.143973867999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4224307273603523</v>
+        <v>0.4642785859559471</v>
       </c>
       <c r="T92">
-        <v>8.698169223102825</v>
+        <v>9.664632470114253</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02609078985646316</v>
+        <v>0.02580407788001852</v>
       </c>
       <c r="W92">
-        <v>0.229647791751846</v>
+        <v>0.2297153984358916</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1185944993475598</v>
+        <v>0.1172912630909932</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9133,22 +9133,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2508260853126966</v>
+        <v>0.2527260853126966</v>
       </c>
       <c r="C93">
-        <v>-14105.10627871689</v>
+        <v>-14341.40601584027</v>
       </c>
       <c r="D93">
-        <v>3661.800721283107</v>
+        <v>3628.177984159732</v>
       </c>
       <c r="E93">
-        <v>17995.007</v>
+        <v>18197.684</v>
       </c>
       <c r="F93">
-        <v>18443.607</v>
+        <v>18646.284</v>
       </c>
       <c r="G93">
         <v>676.7</v>
@@ -9169,37 +9169,37 @@
         <v>510.1</v>
       </c>
       <c r="M93">
-        <v>4349.002530599999</v>
+        <v>4396.7937672</v>
       </c>
       <c r="N93">
-        <v>-3838.902530599999</v>
+        <v>-3886.6937672</v>
       </c>
       <c r="O93">
-        <v>-844.5585567319998</v>
+        <v>-855.072628784</v>
       </c>
       <c r="P93">
-        <v>-2994.343973867999</v>
+        <v>-3031.621138416</v>
       </c>
       <c r="Q93">
-        <v>-2856.143973867999</v>
+        <v>-2893.421138416</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4642785859559471</v>
+        <v>0.5165884092004407</v>
       </c>
       <c r="T93">
-        <v>9.664632470114253</v>
+        <v>10.87271152887854</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02580407788001852</v>
+        <v>0.02552359877262701</v>
       </c>
       <c r="W93">
-        <v>0.2297153984358916</v>
+        <v>0.2297815354094146</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1172912630909932</v>
+        <v>0.1160163580573955</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9215,22 +9215,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2527260853126966</v>
+        <v>0.2546260853126966</v>
       </c>
       <c r="C94">
-        <v>-14341.40601584027</v>
+        <v>-14577.09392134846</v>
       </c>
       <c r="D94">
-        <v>3628.177984159732</v>
+        <v>3595.167078651539</v>
       </c>
       <c r="E94">
-        <v>18197.684</v>
+        <v>18400.361</v>
       </c>
       <c r="F94">
-        <v>18646.284</v>
+        <v>18848.961</v>
       </c>
       <c r="G94">
         <v>676.7</v>
@@ -9251,37 +9251,37 @@
         <v>510.1</v>
       </c>
       <c r="M94">
-        <v>4396.7937672</v>
+        <v>4444.5850038</v>
       </c>
       <c r="N94">
-        <v>-3886.6937672</v>
+        <v>-3934.4850038</v>
       </c>
       <c r="O94">
-        <v>-855.072628784</v>
+        <v>-865.586700836</v>
       </c>
       <c r="P94">
-        <v>-3031.621138416</v>
+        <v>-3068.898302964</v>
       </c>
       <c r="Q94">
-        <v>-2893.421138416</v>
+        <v>-2930.698302964</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5165884092004407</v>
+        <v>0.583843896229075</v>
       </c>
       <c r="T94">
-        <v>10.87271152887854</v>
+        <v>12.42595603300404</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02552359877262701</v>
+        <v>0.02524915147399661</v>
       </c>
       <c r="W94">
-        <v>0.2297815354094146</v>
+        <v>0.2298462500824316</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1160163580573955</v>
+        <v>0.1147688703363482</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9297,22 +9297,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2546260853126966</v>
+        <v>0.2565260853126966</v>
       </c>
       <c r="C95">
-        <v>-14577.09392134846</v>
+        <v>-14812.18654487842</v>
       </c>
       <c r="D95">
-        <v>3595.167078651539</v>
+        <v>3562.751455121582</v>
       </c>
       <c r="E95">
-        <v>18400.361</v>
+        <v>18603.038</v>
       </c>
       <c r="F95">
-        <v>18848.961</v>
+        <v>19051.638</v>
       </c>
       <c r="G95">
         <v>676.7</v>
@@ -9333,37 +9333,37 @@
         <v>510.1</v>
       </c>
       <c r="M95">
-        <v>4444.5850038</v>
+        <v>4492.3762404</v>
       </c>
       <c r="N95">
-        <v>-3934.4850038</v>
+        <v>-3982.2762404</v>
       </c>
       <c r="O95">
-        <v>-865.586700836</v>
+        <v>-876.1007728880001</v>
       </c>
       <c r="P95">
-        <v>-3068.898302964</v>
+        <v>-3106.175467512</v>
       </c>
       <c r="Q95">
-        <v>-2930.698302964</v>
+        <v>-2967.975467512</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.583843896229075</v>
+        <v>0.673517878933921</v>
       </c>
       <c r="T95">
-        <v>12.42595603300404</v>
+        <v>14.49694870517139</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02524915147399661</v>
+        <v>0.02498054347959239</v>
       </c>
       <c r="W95">
-        <v>0.2298462500824316</v>
+        <v>0.2299095878475121</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9371,7 +9371,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1147688703363482</v>
+        <v>0.1135479249072381</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9379,22 +9379,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2565260853126966</v>
+        <v>0.2584260853126966</v>
       </c>
       <c r="C96">
-        <v>-14812.18654487842</v>
+        <v>-15046.69984452517</v>
       </c>
       <c r="D96">
-        <v>3562.751455121582</v>
+        <v>3530.915155474829</v>
       </c>
       <c r="E96">
-        <v>18603.038</v>
+        <v>18805.715</v>
       </c>
       <c r="F96">
-        <v>19051.638</v>
+        <v>19254.315</v>
       </c>
       <c r="G96">
         <v>676.7</v>
@@ -9415,37 +9415,37 @@
         <v>510.1</v>
       </c>
       <c r="M96">
-        <v>4492.3762404</v>
+        <v>4540.167477</v>
       </c>
       <c r="N96">
-        <v>-3982.2762404</v>
+        <v>-4030.067477</v>
       </c>
       <c r="O96">
-        <v>-876.1007728880001</v>
+        <v>-886.61484494</v>
       </c>
       <c r="P96">
-        <v>-3106.175467512</v>
+        <v>-3143.45263206</v>
       </c>
       <c r="Q96">
-        <v>-2967.975467512</v>
+        <v>-3005.25263206</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.673517878933921</v>
+        <v>0.7990614547207057</v>
       </c>
       <c r="T96">
-        <v>14.49694870517139</v>
+        <v>17.39633844620568</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02498054347959239</v>
+        <v>0.02471759039033352</v>
       </c>
       <c r="W96">
-        <v>0.2299095878475121</v>
+        <v>0.2299715921859594</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1135479249072381</v>
+        <v>0.1123526835924251</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9461,22 +9461,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2584260853126966</v>
+        <v>0.2603260853126966</v>
       </c>
       <c r="C97">
-        <v>-15046.69984452517</v>
+        <v>-15280.64921303748</v>
       </c>
       <c r="D97">
-        <v>3530.915155474829</v>
+        <v>3499.642786962518</v>
       </c>
       <c r="E97">
-        <v>18805.715</v>
+        <v>19008.392</v>
       </c>
       <c r="F97">
-        <v>19254.315</v>
+        <v>19456.992</v>
       </c>
       <c r="G97">
         <v>676.7</v>
@@ -9497,37 +9497,37 @@
         <v>510.1</v>
       </c>
       <c r="M97">
-        <v>4540.167477</v>
+        <v>4587.9587136</v>
       </c>
       <c r="N97">
-        <v>-4030.067477</v>
+        <v>-4077.8587136</v>
       </c>
       <c r="O97">
-        <v>-886.61484494</v>
+        <v>-897.128916992</v>
       </c>
       <c r="P97">
-        <v>-3143.45263206</v>
+        <v>-3180.729796608</v>
       </c>
       <c r="Q97">
-        <v>-3005.25263206</v>
+        <v>-3042.529796608</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7990614547207057</v>
+        <v>0.9873768184008824</v>
       </c>
       <c r="T97">
-        <v>17.39633844620568</v>
+        <v>21.7454230577571</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02471759039033352</v>
+        <v>0.02446011549043422</v>
       </c>
       <c r="W97">
-        <v>0.2299715921859594</v>
+        <v>0.2300323047673556</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1123526835924251</v>
+        <v>0.1111823431383373</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9543,22 +9543,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2603260853126966</v>
+        <v>0.2622260853126966</v>
       </c>
       <c r="C98">
-        <v>-15280.64921303748</v>
+        <v>-15514.04950263366</v>
       </c>
       <c r="D98">
-        <v>3499.642786962518</v>
+        <v>3468.919497366342</v>
       </c>
       <c r="E98">
-        <v>19008.392</v>
+        <v>19211.069</v>
       </c>
       <c r="F98">
-        <v>19456.99199999999</v>
+        <v>19659.669</v>
       </c>
       <c r="G98">
         <v>676.7</v>
@@ -9579,37 +9579,37 @@
         <v>510.1</v>
       </c>
       <c r="M98">
-        <v>4587.958713599999</v>
+        <v>4635.7499502</v>
       </c>
       <c r="N98">
-        <v>-4077.858713599999</v>
+        <v>-4125.6499502</v>
       </c>
       <c r="O98">
-        <v>-897.1289169919999</v>
+        <v>-907.6429890439999</v>
       </c>
       <c r="P98">
-        <v>-3180.729796608</v>
+        <v>-3218.006961156</v>
       </c>
       <c r="Q98">
-        <v>-3042.529796608</v>
+        <v>-3079.806961156</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9873768184008799</v>
+        <v>1.30123575786784</v>
       </c>
       <c r="T98">
-        <v>21.74542305775704</v>
+        <v>28.99389741034273</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02446011549043422</v>
+        <v>0.02420794935135757</v>
       </c>
       <c r="W98">
-        <v>0.2300323047673556</v>
+        <v>0.2300917655429499</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1111823431383373</v>
+        <v>0.1100361334152617</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9625,22 +9625,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2622260853126966</v>
+        <v>0.2641260853126967</v>
       </c>
       <c r="C99">
-        <v>-15514.04950263366</v>
+        <v>-15746.91504852159</v>
       </c>
       <c r="D99">
-        <v>3468.919497366342</v>
+        <v>3438.730951478403</v>
       </c>
       <c r="E99">
-        <v>19211.069</v>
+        <v>19413.746</v>
       </c>
       <c r="F99">
-        <v>19659.669</v>
+        <v>19862.346</v>
       </c>
       <c r="G99">
         <v>676.7</v>
@@ -9661,37 +9661,37 @@
         <v>510.1</v>
       </c>
       <c r="M99">
-        <v>4635.7499502</v>
+        <v>4683.5411868</v>
       </c>
       <c r="N99">
-        <v>-4125.6499502</v>
+        <v>-4173.4411868</v>
       </c>
       <c r="O99">
-        <v>-907.6429890439999</v>
+        <v>-918.1570610959999</v>
       </c>
       <c r="P99">
-        <v>-3218.006961156</v>
+        <v>-3255.284125704</v>
       </c>
       <c r="Q99">
-        <v>-3079.806961156</v>
+        <v>-3117.084125704</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.30123575786784</v>
+        <v>1.92895363680176</v>
       </c>
       <c r="T99">
-        <v>28.99389741034273</v>
+        <v>43.49084611551409</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02420794935135757</v>
+        <v>0.02396092946001719</v>
       </c>
       <c r="W99">
-        <v>0.2300917655429499</v>
+        <v>0.230150012833328</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1100361334152617</v>
+        <v>0.108913315727351</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9707,22 +9707,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2641260853126967</v>
+        <v>0.2660260853126966</v>
       </c>
       <c r="C100">
-        <v>-15746.91504852159</v>
+        <v>-15979.25969120131</v>
       </c>
       <c r="D100">
-        <v>3438.730951478403</v>
+        <v>3409.063308798691</v>
       </c>
       <c r="E100">
-        <v>19413.746</v>
+        <v>19616.423</v>
       </c>
       <c r="F100">
-        <v>19862.346</v>
+        <v>20065.023</v>
       </c>
       <c r="G100">
         <v>676.7</v>
@@ -9743,37 +9743,37 @@
         <v>510.1</v>
       </c>
       <c r="M100">
-        <v>4683.5411868</v>
+        <v>4731.332423399999</v>
       </c>
       <c r="N100">
-        <v>-4173.4411868</v>
+        <v>-4221.232423399999</v>
       </c>
       <c r="O100">
-        <v>-918.1570610959999</v>
+        <v>-928.6711331479997</v>
       </c>
       <c r="P100">
-        <v>-3255.284125704</v>
+        <v>-3292.561290251999</v>
       </c>
       <c r="Q100">
-        <v>-3117.084125704</v>
+        <v>-3154.361290251999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.92895363680176</v>
+        <v>3.81210727360352</v>
       </c>
       <c r="T100">
-        <v>43.49084611551409</v>
+        <v>86.98169223102818</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02396092946001719</v>
+        <v>0.02371889986951197</v>
       </c>
       <c r="W100">
-        <v>0.230150012833328</v>
+        <v>0.2302070834107691</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9781,91 +9781,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.108913315727351</v>
+        <v>0.1078131812250545</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2660260853126966</v>
-      </c>
-      <c r="C101">
-        <v>-15979.25969120131</v>
-      </c>
-      <c r="D101">
-        <v>3409.063308798691</v>
-      </c>
-      <c r="E101">
-        <v>19616.423</v>
-      </c>
-      <c r="F101">
-        <v>20065.023</v>
-      </c>
-      <c r="G101">
-        <v>676.7</v>
-      </c>
-      <c r="H101">
-        <v>19819.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>648.3</v>
-      </c>
-      <c r="K101">
-        <v>138.2</v>
-      </c>
-      <c r="L101">
-        <v>510.1</v>
-      </c>
-      <c r="M101">
-        <v>4731.332423399999</v>
-      </c>
-      <c r="N101">
-        <v>-4221.232423399999</v>
-      </c>
-      <c r="O101">
-        <v>-928.6711331479997</v>
-      </c>
-      <c r="P101">
-        <v>-3292.561290251999</v>
-      </c>
-      <c r="Q101">
-        <v>-3154.361290251999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.81210727360352</v>
-      </c>
-      <c r="T101">
-        <v>86.98169223102818</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02371889986951197</v>
-      </c>
-      <c r="W101">
-        <v>0.2302070834107691</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1078131812250545</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
